--- a/research/traditional_assets/database/data/austria/austria_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_retail_distributors.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0739410312689488</v>
+        <v>0.07379777279390333</v>
       </c>
       <c r="C2">
-        <v>271.5992844393753</v>
+        <v>269.7214090880466</v>
       </c>
       <c r="D2">
-        <v>264.8392844393753</v>
+        <v>266.1944090880467</v>
       </c>
       <c r="E2">
-        <v>-146</v>
+        <v>-142.767</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.233</v>
       </c>
       <c r="G2">
         <v>6.76</v>
@@ -1445,28 +1445,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1626199</v>
       </c>
       <c r="N2">
-        <v>13.96666666666666</v>
+        <v>13.80404676666666</v>
       </c>
       <c r="O2">
-        <v>3.351999999999999</v>
+        <v>3.312971223999999</v>
       </c>
       <c r="P2">
-        <v>10.61466666666666</v>
+        <v>10.49107554266666</v>
       </c>
       <c r="Q2">
-        <v>47.31466666666667</v>
+        <v>47.19107554266667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0739410312689488</v>
+        <v>0.07415706342818518</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5830510704098794</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>85.88534777519027</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07379777279390333</v>
+        <v>0.07365451431885783</v>
       </c>
       <c r="C3">
-        <v>269.7214090880466</v>
+        <v>267.857472812334</v>
       </c>
       <c r="D3">
-        <v>266.1944090880467</v>
+        <v>267.563472812334</v>
       </c>
       <c r="E3">
-        <v>-142.767</v>
+        <v>-139.534</v>
       </c>
       <c r="F3">
-        <v>3.233</v>
+        <v>6.466</v>
       </c>
       <c r="G3">
         <v>6.76</v>
@@ -1527,28 +1527,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M3">
-        <v>0.1626199</v>
+        <v>0.3252398</v>
       </c>
       <c r="N3">
-        <v>13.80404676666666</v>
+        <v>13.64142686666666</v>
       </c>
       <c r="O3">
-        <v>3.312971223999999</v>
+        <v>3.273942447999998</v>
       </c>
       <c r="P3">
-        <v>10.49107554266666</v>
+        <v>10.36748441866666</v>
       </c>
       <c r="Q3">
-        <v>47.19107554266667</v>
+        <v>47.06748441866667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07415706342818518</v>
+        <v>0.07437750440699779</v>
       </c>
       <c r="T3">
-        <v>0.5830510704098794</v>
+        <v>0.5875835689524171</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>85.88534777519027</v>
+        <v>42.94267388759513</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07365451431885783</v>
+        <v>0.07351125584381236</v>
       </c>
       <c r="C4">
-        <v>267.857472812334</v>
+        <v>266.0076917941444</v>
       </c>
       <c r="D4">
-        <v>267.563472812334</v>
+        <v>268.9466917941444</v>
       </c>
       <c r="E4">
-        <v>-139.534</v>
+        <v>-136.301</v>
       </c>
       <c r="F4">
-        <v>6.466</v>
+        <v>9.699</v>
       </c>
       <c r="G4">
         <v>6.76</v>
@@ -1609,28 +1609,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M4">
-        <v>0.3252398</v>
+        <v>0.4878597</v>
       </c>
       <c r="N4">
-        <v>13.64142686666666</v>
+        <v>13.47880696666666</v>
       </c>
       <c r="O4">
-        <v>3.273942447999998</v>
+        <v>3.234913671999999</v>
       </c>
       <c r="P4">
-        <v>10.36748441866666</v>
+        <v>10.24389329466666</v>
       </c>
       <c r="Q4">
-        <v>47.06748441866667</v>
+        <v>46.94389329466667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07437750440699779</v>
+        <v>0.07460249056063131</v>
       </c>
       <c r="T4">
-        <v>0.5875835689524171</v>
+        <v>0.5922095210731518</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.94267388759513</v>
+        <v>28.62844925839676</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07351125584381236</v>
+        <v>0.07336799736876688</v>
       </c>
       <c r="C5">
-        <v>266.0076917941444</v>
+        <v>264.172286708986</v>
       </c>
       <c r="D5">
-        <v>268.9466917941444</v>
+        <v>270.344286708986</v>
       </c>
       <c r="E5">
-        <v>-136.301</v>
+        <v>-133.068</v>
       </c>
       <c r="F5">
-        <v>9.699</v>
+        <v>12.932</v>
       </c>
       <c r="G5">
         <v>6.76</v>
@@ -1691,28 +1691,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M5">
-        <v>0.4878597</v>
+        <v>0.6504795999999999</v>
       </c>
       <c r="N5">
-        <v>13.47880696666666</v>
+        <v>13.31618706666666</v>
       </c>
       <c r="O5">
-        <v>3.234913671999999</v>
+        <v>3.195884895999999</v>
       </c>
       <c r="P5">
-        <v>10.24389329466666</v>
+        <v>10.12030217066666</v>
       </c>
       <c r="Q5">
-        <v>46.94389329466667</v>
+        <v>46.82030217066666</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07460249056063131</v>
+        <v>0.07483216392579885</v>
       </c>
       <c r="T5">
-        <v>0.5922095210731518</v>
+        <v>0.5969318471964017</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.62844925839676</v>
+        <v>21.47133694379756</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07336799736876688</v>
+        <v>0.0732247388937214</v>
       </c>
       <c r="C6">
-        <v>264.172286708986</v>
+        <v>262.351482843333</v>
       </c>
       <c r="D6">
-        <v>270.344286708986</v>
+        <v>271.756482843333</v>
       </c>
       <c r="E6">
-        <v>-133.068</v>
+        <v>-129.835</v>
       </c>
       <c r="F6">
-        <v>12.932</v>
+        <v>16.165</v>
       </c>
       <c r="G6">
         <v>6.76</v>
@@ -1773,28 +1773,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M6">
-        <v>0.6504795999999999</v>
+        <v>0.8130995000000001</v>
       </c>
       <c r="N6">
-        <v>13.31618706666666</v>
+        <v>13.15356716666666</v>
       </c>
       <c r="O6">
-        <v>3.195884895999999</v>
+        <v>3.156856119999999</v>
       </c>
       <c r="P6">
-        <v>10.12030217066666</v>
+        <v>9.996711046666663</v>
       </c>
       <c r="Q6">
-        <v>46.82030217066666</v>
+        <v>46.69671104666666</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07483216392579885</v>
+        <v>0.07506667251970675</v>
       </c>
       <c r="T6">
-        <v>0.5969318471964017</v>
+        <v>0.6017535907117199</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.47133694379756</v>
+        <v>17.17706955503805</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0732247388937214</v>
+        <v>0.07308148041867593</v>
       </c>
       <c r="C7">
-        <v>262.351482843333</v>
+        <v>260.5455102156894</v>
       </c>
       <c r="D7">
-        <v>271.756482843333</v>
+        <v>273.1835102156894</v>
       </c>
       <c r="E7">
-        <v>-129.835</v>
+        <v>-126.602</v>
       </c>
       <c r="F7">
-        <v>16.165</v>
+        <v>19.398</v>
       </c>
       <c r="G7">
         <v>6.76</v>
@@ -1855,28 +1855,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M7">
-        <v>0.8130995000000001</v>
+        <v>0.9757194000000001</v>
       </c>
       <c r="N7">
-        <v>13.15356716666666</v>
+        <v>12.99094726666666</v>
       </c>
       <c r="O7">
-        <v>3.156856119999999</v>
+        <v>3.117827343999998</v>
       </c>
       <c r="P7">
-        <v>9.996711046666663</v>
+        <v>9.873119922666662</v>
       </c>
       <c r="Q7">
-        <v>46.69671104666666</v>
+        <v>46.57311992266666</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07506667251970675</v>
+        <v>0.07530617065816589</v>
       </c>
       <c r="T7">
-        <v>0.6017535907117199</v>
+        <v>0.6066779245145981</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.17706955503805</v>
+        <v>14.31422462919837</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07308148041867593</v>
+        <v>0.07301802194363045</v>
       </c>
       <c r="C8">
-        <v>260.5455102156894</v>
+        <v>257.9494341259486</v>
       </c>
       <c r="D8">
-        <v>273.1835102156894</v>
+        <v>273.8204341259486</v>
       </c>
       <c r="E8">
-        <v>-126.602</v>
+        <v>-123.369</v>
       </c>
       <c r="F8">
-        <v>19.398</v>
+        <v>22.631</v>
       </c>
       <c r="G8">
         <v>6.76</v>
@@ -1937,45 +1937,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M8">
-        <v>0.9757193999999999</v>
+        <v>1.1722858</v>
       </c>
       <c r="N8">
-        <v>12.99094726666666</v>
+        <v>12.79438086666666</v>
       </c>
       <c r="O8">
-        <v>3.117827343999999</v>
+        <v>3.070651407999998</v>
       </c>
       <c r="P8">
-        <v>9.873119922666664</v>
+        <v>9.723729458666662</v>
       </c>
       <c r="Q8">
-        <v>46.57311992266666</v>
+        <v>46.42372945866666</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07530617065816589</v>
+        <v>0.0755508192942263</v>
       </c>
       <c r="T8">
-        <v>0.6066779245145981</v>
+        <v>0.6117081579691511</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.31422462919838</v>
+        <v>11.91404576142325</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07301802194363045</v>
+        <v>0.07288616346858498</v>
       </c>
       <c r="C9">
-        <v>257.9494341259486</v>
+        <v>256.0494226432044</v>
       </c>
       <c r="D9">
-        <v>273.8204341259486</v>
+        <v>275.1534226432044</v>
       </c>
       <c r="E9">
-        <v>-123.369</v>
+        <v>-120.136</v>
       </c>
       <c r="F9">
-        <v>22.631</v>
+        <v>25.864</v>
       </c>
       <c r="G9">
         <v>6.76</v>
@@ -2019,28 +2019,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M9">
-        <v>1.1722858</v>
+        <v>1.3397552</v>
       </c>
       <c r="N9">
-        <v>12.79438086666666</v>
+        <v>12.62691146666666</v>
       </c>
       <c r="O9">
-        <v>3.070651407999998</v>
+        <v>3.030458751999999</v>
       </c>
       <c r="P9">
-        <v>9.723729458666662</v>
+        <v>9.596452714666663</v>
       </c>
       <c r="Q9">
-        <v>46.42372945866666</v>
+        <v>46.29645271466666</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0755508192942263</v>
+        <v>0.07580078637889671</v>
       </c>
       <c r="T9">
-        <v>0.6117081579691511</v>
+        <v>0.6168477443248901</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.91404576142324</v>
+        <v>10.42479004124534</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07288616346858498</v>
+        <v>0.07287058499353949</v>
       </c>
       <c r="C10">
-        <v>256.0494226432044</v>
+        <v>252.9747668655163</v>
       </c>
       <c r="D10">
-        <v>275.1534226432044</v>
+        <v>275.3117668655163</v>
       </c>
       <c r="E10">
-        <v>-120.136</v>
+        <v>-116.903</v>
       </c>
       <c r="F10">
-        <v>25.864</v>
+        <v>29.097</v>
       </c>
       <c r="G10">
         <v>6.76</v>
@@ -2101,45 +2101,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M10">
-        <v>1.3397552</v>
+        <v>1.5566895</v>
       </c>
       <c r="N10">
-        <v>12.62691146666666</v>
+        <v>12.40997716666666</v>
       </c>
       <c r="O10">
-        <v>3.030458751999999</v>
+        <v>2.978394519999998</v>
       </c>
       <c r="P10">
-        <v>9.596452714666663</v>
+        <v>9.431582646666662</v>
       </c>
       <c r="Q10">
-        <v>46.29645271466666</v>
+        <v>46.13158264666666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07580078637889671</v>
+        <v>0.0760562472456478</v>
       </c>
       <c r="T10">
-        <v>0.6168477443248901</v>
+        <v>0.6221002886225134</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.42479004124534</v>
+        <v>8.972031138301286</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07287058499353949</v>
+        <v>0.07275164651849403</v>
       </c>
       <c r="C11">
-        <v>252.9747668655163</v>
+        <v>250.9567264669857</v>
       </c>
       <c r="D11">
-        <v>275.3117668655163</v>
+        <v>276.5267264669857</v>
       </c>
       <c r="E11">
-        <v>-116.903</v>
+        <v>-113.67</v>
       </c>
       <c r="F11">
-        <v>29.097</v>
+        <v>32.33</v>
       </c>
       <c r="G11">
         <v>6.76</v>
@@ -2183,28 +2183,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M11">
-        <v>1.5566895</v>
+        <v>1.729655</v>
       </c>
       <c r="N11">
-        <v>12.40997716666666</v>
+        <v>12.23701166666666</v>
       </c>
       <c r="O11">
-        <v>2.978394519999998</v>
+        <v>2.936882799999999</v>
       </c>
       <c r="P11">
-        <v>9.431582646666662</v>
+        <v>9.300128866666663</v>
       </c>
       <c r="Q11">
-        <v>46.13158264666666</v>
+        <v>46.00012886666666</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0760562472456478</v>
+        <v>0.07631738502054891</v>
       </c>
       <c r="T11">
-        <v>0.6221002886225134</v>
+        <v>0.6274695561267507</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.972031138301286</v>
+        <v>8.074828024471159</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07275164651849403</v>
+        <v>0.07269958804344855</v>
       </c>
       <c r="C12">
-        <v>250.9567264669857</v>
+        <v>248.2588855804241</v>
       </c>
       <c r="D12">
-        <v>276.5267264669857</v>
+        <v>277.0618855804241</v>
       </c>
       <c r="E12">
-        <v>-113.67</v>
+        <v>-110.437</v>
       </c>
       <c r="F12">
-        <v>32.33000000000001</v>
+        <v>35.563</v>
       </c>
       <c r="G12">
         <v>6.76</v>
@@ -2265,45 +2265,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M12">
-        <v>1.729655</v>
+        <v>1.9310709</v>
       </c>
       <c r="N12">
-        <v>12.23701166666666</v>
+        <v>12.03559576666666</v>
       </c>
       <c r="O12">
-        <v>2.936882799999998</v>
+        <v>2.888542983999999</v>
       </c>
       <c r="P12">
-        <v>9.300128866666661</v>
+        <v>9.147052782666663</v>
       </c>
       <c r="Q12">
-        <v>46.00012886666666</v>
+        <v>45.84705278266667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07631738502054891</v>
+        <v>0.07658439106005455</v>
       </c>
       <c r="T12">
-        <v>0.6274695561267507</v>
+        <v>0.6329594813277123</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.24</v>
       </c>
       <c r="W12">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.074828024471156</v>
+        <v>7.232601696119319</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07269958804344855</v>
+        <v>0.07258672956840306</v>
       </c>
       <c r="C13">
-        <v>248.2588855804241</v>
+        <v>246.1932091919156</v>
       </c>
       <c r="D13">
-        <v>277.0618855804241</v>
+        <v>278.2292091919156</v>
       </c>
       <c r="E13">
-        <v>-110.437</v>
+        <v>-107.204</v>
       </c>
       <c r="F13">
-        <v>35.563</v>
+        <v>38.796</v>
       </c>
       <c r="G13">
         <v>6.76</v>
@@ -2347,28 +2347,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M13">
-        <v>1.9310709</v>
+        <v>2.1066228</v>
       </c>
       <c r="N13">
-        <v>12.03559576666666</v>
+        <v>11.86004386666666</v>
       </c>
       <c r="O13">
-        <v>2.888542983999999</v>
+        <v>2.846410527999998</v>
       </c>
       <c r="P13">
-        <v>9.147052782666663</v>
+        <v>9.013633338666663</v>
       </c>
       <c r="Q13">
-        <v>45.84705278266667</v>
+        <v>45.71363333866667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07658439106005455</v>
+        <v>0.07685746541863984</v>
       </c>
       <c r="T13">
-        <v>0.6329594813277123</v>
+        <v>0.6385741775559685</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.232601696119319</v>
+        <v>6.629884888109377</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07258672956840306</v>
+        <v>0.07247387109335758</v>
       </c>
       <c r="C14">
-        <v>246.1932091919156</v>
+        <v>244.1374108119058</v>
       </c>
       <c r="D14">
-        <v>278.2292091919156</v>
+        <v>279.4064108119058</v>
       </c>
       <c r="E14">
-        <v>-107.204</v>
+        <v>-103.971</v>
       </c>
       <c r="F14">
-        <v>38.796</v>
+        <v>42.029</v>
       </c>
       <c r="G14">
         <v>6.76</v>
@@ -2429,28 +2429,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M14">
-        <v>2.1066228</v>
+        <v>2.2821747</v>
       </c>
       <c r="N14">
-        <v>11.86004386666666</v>
+        <v>11.68449196666666</v>
       </c>
       <c r="O14">
-        <v>2.846410527999998</v>
+        <v>2.804278071999998</v>
       </c>
       <c r="P14">
-        <v>9.013633338666663</v>
+        <v>8.880213894666662</v>
       </c>
       <c r="Q14">
-        <v>45.71363333866667</v>
+        <v>45.58021389466666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07685746541863984</v>
+        <v>0.07713681734868688</v>
       </c>
       <c r="T14">
-        <v>0.6385741775559685</v>
+        <v>0.6443179472607363</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.629884888109377</v>
+        <v>6.119893742870193</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07247387109335758</v>
+        <v>0.07246741261831212</v>
       </c>
       <c r="C15">
-        <v>244.1374108119058</v>
+        <v>240.9720791439483</v>
       </c>
       <c r="D15">
-        <v>279.4064108119058</v>
+        <v>279.4740791439483</v>
       </c>
       <c r="E15">
-        <v>-103.971</v>
+        <v>-100.738</v>
       </c>
       <c r="F15">
-        <v>42.029</v>
+        <v>45.26200000000001</v>
       </c>
       <c r="G15">
         <v>6.76</v>
@@ -2511,45 +2511,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M15">
-        <v>2.2821747</v>
+        <v>2.502988600000001</v>
       </c>
       <c r="N15">
-        <v>11.68449196666666</v>
+        <v>11.46367806666666</v>
       </c>
       <c r="O15">
-        <v>2.804278071999998</v>
+        <v>2.751282735999999</v>
       </c>
       <c r="P15">
-        <v>8.880213894666662</v>
+        <v>8.712395330666663</v>
       </c>
       <c r="Q15">
-        <v>45.58021389466666</v>
+        <v>45.41239533066667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07713681734868688</v>
+        <v>0.07742266583524665</v>
       </c>
       <c r="T15">
-        <v>0.6443179472607363</v>
+        <v>0.6501952930051499</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.119893742870193</v>
+        <v>5.579996116109621</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07246741261831212</v>
+        <v>0.07236215414326663</v>
       </c>
       <c r="C16">
-        <v>240.9720791439483</v>
+        <v>238.8465576724881</v>
       </c>
       <c r="D16">
-        <v>279.4740791439483</v>
+        <v>280.5815576724881</v>
       </c>
       <c r="E16">
-        <v>-100.738</v>
+        <v>-97.505</v>
       </c>
       <c r="F16">
-        <v>45.26200000000001</v>
+        <v>48.49500000000001</v>
       </c>
       <c r="G16">
         <v>6.76</v>
@@ -2593,28 +2593,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M16">
-        <v>2.502988600000001</v>
+        <v>2.681773500000001</v>
       </c>
       <c r="N16">
-        <v>11.46367806666666</v>
+        <v>11.28489316666666</v>
       </c>
       <c r="O16">
-        <v>2.751282735999999</v>
+        <v>2.708374359999999</v>
       </c>
       <c r="P16">
-        <v>8.712395330666663</v>
+        <v>8.576518806666662</v>
       </c>
       <c r="Q16">
-        <v>45.41239533066667</v>
+        <v>45.27651880666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07742266583524665</v>
+        <v>0.07771524016854899</v>
       </c>
       <c r="T16">
-        <v>0.6501952930051499</v>
+        <v>0.6562109292376674</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.579996116109621</v>
+        <v>5.207996375035647</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07236215414326663</v>
+        <v>0.07225689566822117</v>
       </c>
       <c r="C17">
-        <v>238.8465576724881</v>
+        <v>236.7298483838719</v>
       </c>
       <c r="D17">
-        <v>280.5815576724881</v>
+        <v>281.6978483838719</v>
       </c>
       <c r="E17">
-        <v>-97.505</v>
+        <v>-94.27199999999999</v>
       </c>
       <c r="F17">
-        <v>48.495</v>
+        <v>51.728</v>
       </c>
       <c r="G17">
         <v>6.76</v>
@@ -2675,28 +2675,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M17">
-        <v>2.6817735</v>
+        <v>2.8605584</v>
       </c>
       <c r="N17">
-        <v>11.28489316666666</v>
+        <v>11.10610826666666</v>
       </c>
       <c r="O17">
-        <v>2.708374359999999</v>
+        <v>2.665465983999999</v>
       </c>
       <c r="P17">
-        <v>8.576518806666662</v>
+        <v>8.440642282666662</v>
       </c>
       <c r="Q17">
-        <v>45.27651880666667</v>
+        <v>45.14064228266666</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07771524016854899</v>
+        <v>0.07801478055740615</v>
       </c>
       <c r="T17">
-        <v>0.6562109292376673</v>
+        <v>0.6623697949042925</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.207996375035647</v>
+        <v>4.882496601595919</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07225689566822117</v>
+        <v>0.07215163719317569</v>
       </c>
       <c r="C18">
-        <v>236.7298483838719</v>
+        <v>234.6220568757436</v>
       </c>
       <c r="D18">
-        <v>281.6978483838719</v>
+        <v>282.8230568757436</v>
       </c>
       <c r="E18">
-        <v>-94.27199999999999</v>
+        <v>-91.03899999999999</v>
       </c>
       <c r="F18">
-        <v>51.728</v>
+        <v>54.96100000000001</v>
       </c>
       <c r="G18">
         <v>6.76</v>
@@ -2757,28 +2757,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M18">
-        <v>2.8605584</v>
+        <v>3.039343300000001</v>
       </c>
       <c r="N18">
-        <v>11.10610826666666</v>
+        <v>10.92732336666666</v>
       </c>
       <c r="O18">
-        <v>2.665465983999999</v>
+        <v>2.622557607999998</v>
       </c>
       <c r="P18">
-        <v>8.440642282666662</v>
+        <v>8.304765758666662</v>
       </c>
       <c r="Q18">
-        <v>45.14064228266666</v>
+        <v>45.00476575866666</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07801478055740615</v>
+        <v>0.07832153878695866</v>
       </c>
       <c r="T18">
-        <v>0.6623697949042925</v>
+        <v>0.6686770669725228</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.882496601595919</v>
+        <v>4.5952909191491</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07215163719317569</v>
+        <v>0.07238837871813021</v>
       </c>
       <c r="C19">
-        <v>234.6220568757436</v>
+        <v>228.8708152602288</v>
       </c>
       <c r="D19">
-        <v>282.8230568757436</v>
+        <v>280.3048152602288</v>
       </c>
       <c r="E19">
-        <v>-91.03899999999999</v>
+        <v>-87.80599999999998</v>
       </c>
       <c r="F19">
-        <v>54.96100000000001</v>
+        <v>58.19400000000001</v>
       </c>
       <c r="G19">
         <v>6.76</v>
@@ -2839,45 +2839,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M19">
-        <v>3.039343300000001</v>
+        <v>3.363613200000001</v>
       </c>
       <c r="N19">
-        <v>10.92732336666666</v>
+        <v>10.60305346666666</v>
       </c>
       <c r="O19">
-        <v>2.622557607999998</v>
+        <v>2.544732831999998</v>
       </c>
       <c r="P19">
-        <v>8.304765758666662</v>
+        <v>8.058320634666661</v>
       </c>
       <c r="Q19">
-        <v>45.00476575866666</v>
+        <v>44.75832063466666</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07832153878695866</v>
+        <v>0.07863577892454904</v>
       </c>
       <c r="T19">
-        <v>0.6686770669725228</v>
+        <v>0.6751381749448565</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.5952909191491</v>
+        <v>4.15228084687819</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07238837871813023</v>
+        <v>0.07280752024308473</v>
       </c>
       <c r="C20">
-        <v>228.8708152602286</v>
+        <v>221.2876421727773</v>
       </c>
       <c r="D20">
-        <v>280.3048152602286</v>
+        <v>275.9546421727773</v>
       </c>
       <c r="E20">
-        <v>-87.806</v>
+        <v>-84.57300000000001</v>
       </c>
       <c r="F20">
-        <v>58.194</v>
+        <v>61.427</v>
       </c>
       <c r="G20">
         <v>6.76</v>
@@ -2921,45 +2921,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M20">
-        <v>3.363613200000001</v>
+        <v>3.7654751</v>
       </c>
       <c r="N20">
-        <v>10.60305346666666</v>
+        <v>10.20119156666666</v>
       </c>
       <c r="O20">
-        <v>2.544732831999999</v>
+        <v>2.448285975999999</v>
       </c>
       <c r="P20">
-        <v>8.058320634666662</v>
+        <v>7.752905590666662</v>
       </c>
       <c r="Q20">
-        <v>44.75832063466667</v>
+        <v>44.45290559066667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07863577892454904</v>
+        <v>0.07895777807788237</v>
       </c>
       <c r="T20">
-        <v>0.6751381749448564</v>
+        <v>0.6817588164473711</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.15228084687819</v>
+        <v>3.709137969513239</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07280752024308473</v>
+        <v>0.07274786176803925</v>
       </c>
       <c r="C21">
-        <v>221.2876421727773</v>
+        <v>218.6655638583439</v>
       </c>
       <c r="D21">
-        <v>275.9546421727773</v>
+        <v>276.565563858344</v>
       </c>
       <c r="E21">
-        <v>-84.57300000000001</v>
+        <v>-81.33999999999999</v>
       </c>
       <c r="F21">
-        <v>61.427</v>
+        <v>64.66000000000001</v>
       </c>
       <c r="G21">
         <v>6.76</v>
@@ -3003,28 +3003,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M21">
-        <v>3.7654751</v>
+        <v>3.963658000000001</v>
       </c>
       <c r="N21">
-        <v>10.20119156666666</v>
+        <v>10.00300866666666</v>
       </c>
       <c r="O21">
-        <v>2.448285975999999</v>
+        <v>2.400722079999999</v>
       </c>
       <c r="P21">
-        <v>7.752905590666662</v>
+        <v>7.602286586666662</v>
       </c>
       <c r="Q21">
-        <v>44.45290559066667</v>
+        <v>44.30228658666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07895777807788237</v>
+        <v>0.07928782721004907</v>
       </c>
       <c r="T21">
-        <v>0.6817588164473711</v>
+        <v>0.6885449739874486</v>
       </c>
       <c r="U21">
         <v>0.0613</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.709137969513239</v>
+        <v>3.523681071037577</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07274786176803925</v>
+        <v>0.07313508329299376</v>
       </c>
       <c r="C22">
-        <v>218.6655638583439</v>
+        <v>211.5148095848613</v>
       </c>
       <c r="D22">
-        <v>276.565563858344</v>
+        <v>272.6478095848614</v>
       </c>
       <c r="E22">
-        <v>-81.33999999999999</v>
+        <v>-78.10699999999999</v>
       </c>
       <c r="F22">
-        <v>64.66000000000001</v>
+        <v>67.89300000000001</v>
       </c>
       <c r="G22">
         <v>6.76</v>
@@ -3085,45 +3085,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M22">
-        <v>3.963658000000001</v>
+        <v>4.351941300000001</v>
       </c>
       <c r="N22">
-        <v>10.00300866666666</v>
+        <v>9.614725366666661</v>
       </c>
       <c r="O22">
-        <v>2.400722079999999</v>
+        <v>2.307534087999999</v>
       </c>
       <c r="P22">
-        <v>7.602286586666662</v>
+        <v>7.307191278666663</v>
       </c>
       <c r="Q22">
-        <v>44.30228658666667</v>
+        <v>44.00719127866667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07928782721004907</v>
+        <v>0.07962623201644781</v>
       </c>
       <c r="T22">
-        <v>0.6885449739874486</v>
+        <v>0.695502932984237</v>
       </c>
       <c r="U22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.523681071037577</v>
+        <v>3.209295738126491</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07313508329299376</v>
+        <v>0.0730967048179483</v>
       </c>
       <c r="C23">
-        <v>211.5148095848614</v>
+        <v>208.665145493944</v>
       </c>
       <c r="D23">
-        <v>272.6478095848614</v>
+        <v>273.0311454939441</v>
       </c>
       <c r="E23">
-        <v>-78.107</v>
+        <v>-74.874</v>
       </c>
       <c r="F23">
-        <v>67.893</v>
+        <v>71.126</v>
       </c>
       <c r="G23">
         <v>6.76</v>
@@ -3167,28 +3167,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M23">
-        <v>4.3519413</v>
+        <v>4.559176600000001</v>
       </c>
       <c r="N23">
-        <v>9.614725366666661</v>
+        <v>9.407490066666661</v>
       </c>
       <c r="O23">
-        <v>2.307534087999999</v>
+        <v>2.257797615999999</v>
       </c>
       <c r="P23">
-        <v>7.307191278666663</v>
+        <v>7.149692450666662</v>
       </c>
       <c r="Q23">
-        <v>44.00719127866667</v>
+        <v>43.84969245066667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07962623201644781</v>
+        <v>0.07997331386916448</v>
       </c>
       <c r="T23">
-        <v>0.695502932984237</v>
+        <v>0.7026393011860714</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.209295738126491</v>
+        <v>3.063418659120741</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0730967048179483</v>
+        <v>0.07442176634290283</v>
       </c>
       <c r="C24">
-        <v>208.665145493944</v>
+        <v>192.7920078562473</v>
       </c>
       <c r="D24">
-        <v>273.0311454939441</v>
+        <v>260.3910078562473</v>
       </c>
       <c r="E24">
-        <v>-74.874</v>
+        <v>-71.64099999999999</v>
       </c>
       <c r="F24">
-        <v>71.126</v>
+        <v>74.35900000000001</v>
       </c>
       <c r="G24">
         <v>6.76</v>
@@ -3249,45 +3249,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M24">
-        <v>4.559176600000001</v>
+        <v>5.346412100000001</v>
       </c>
       <c r="N24">
-        <v>9.407490066666661</v>
+        <v>8.620254566666659</v>
       </c>
       <c r="O24">
-        <v>2.257797615999999</v>
+        <v>2.068861095999998</v>
       </c>
       <c r="P24">
-        <v>7.149692450666662</v>
+        <v>6.551393470666661</v>
       </c>
       <c r="Q24">
-        <v>43.84969245066667</v>
+        <v>43.25139347066666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07997331386916448</v>
+        <v>0.08032941083493873</v>
       </c>
       <c r="T24">
-        <v>0.7026393011860714</v>
+        <v>0.7099610296009403</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.063418659120741</v>
+        <v>2.612343830859327</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07442176634290283</v>
+        <v>0.07444266786785735</v>
       </c>
       <c r="C25">
-        <v>192.7920078562473</v>
+        <v>189.368991717606</v>
       </c>
       <c r="D25">
-        <v>260.3910078562473</v>
+        <v>260.200991717606</v>
       </c>
       <c r="E25">
-        <v>-71.64099999999999</v>
+        <v>-68.40799999999999</v>
       </c>
       <c r="F25">
-        <v>74.35900000000001</v>
+        <v>77.59200000000001</v>
       </c>
       <c r="G25">
         <v>6.76</v>
@@ -3331,28 +3331,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M25">
-        <v>5.346412100000001</v>
+        <v>5.578864800000002</v>
       </c>
       <c r="N25">
-        <v>8.620254566666659</v>
+        <v>8.38780186666666</v>
       </c>
       <c r="O25">
-        <v>2.068861095999998</v>
+        <v>2.013072447999998</v>
       </c>
       <c r="P25">
-        <v>6.551393470666661</v>
+        <v>6.374729418666662</v>
       </c>
       <c r="Q25">
-        <v>43.25139347066666</v>
+        <v>43.07472941866666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08032941083493873</v>
+        <v>0.0806948787734965</v>
       </c>
       <c r="T25">
-        <v>0.7099610296009403</v>
+        <v>0.7174754350793583</v>
       </c>
       <c r="U25">
         <v>0.07190000000000001</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.612343830859327</v>
+        <v>2.503496171240188</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07444266786785735</v>
+        <v>0.07520456939281188</v>
       </c>
       <c r="C26">
-        <v>189.368991717606</v>
+        <v>179.3939262332942</v>
       </c>
       <c r="D26">
-        <v>260.200991717606</v>
+        <v>253.4589262332942</v>
       </c>
       <c r="E26">
-        <v>-68.408</v>
+        <v>-65.175</v>
       </c>
       <c r="F26">
-        <v>77.592</v>
+        <v>80.825</v>
       </c>
       <c r="G26">
         <v>6.76</v>
@@ -3413,45 +3413,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M26">
-        <v>5.578864800000001</v>
+        <v>6.126535000000001</v>
       </c>
       <c r="N26">
-        <v>8.38780186666666</v>
+        <v>7.840131666666661</v>
       </c>
       <c r="O26">
-        <v>2.013072447999998</v>
+        <v>1.881631599999999</v>
       </c>
       <c r="P26">
-        <v>6.374729418666662</v>
+        <v>5.958500066666662</v>
       </c>
       <c r="Q26">
-        <v>43.07472941866666</v>
+        <v>42.65850006666666</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0806948787734965</v>
+        <v>0.08107009252374917</v>
       </c>
       <c r="T26">
-        <v>0.7174754350793583</v>
+        <v>0.7251902247038676</v>
       </c>
       <c r="U26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.503496171240188</v>
+        <v>2.279700787911382</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07520456939281188</v>
+        <v>0.07525511091776638</v>
       </c>
       <c r="C27">
-        <v>179.3939262332942</v>
+        <v>175.7260203631067</v>
       </c>
       <c r="D27">
-        <v>253.4589262332942</v>
+        <v>253.0240203631067</v>
       </c>
       <c r="E27">
-        <v>-65.175</v>
+        <v>-61.94199999999999</v>
       </c>
       <c r="F27">
-        <v>80.825</v>
+        <v>84.05800000000001</v>
       </c>
       <c r="G27">
         <v>6.76</v>
@@ -3495,28 +3495,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M27">
-        <v>6.126535000000001</v>
+        <v>6.371596400000001</v>
       </c>
       <c r="N27">
-        <v>7.840131666666661</v>
+        <v>7.59507026666666</v>
       </c>
       <c r="O27">
-        <v>1.881631599999999</v>
+        <v>1.822816863999998</v>
       </c>
       <c r="P27">
-        <v>5.958500066666662</v>
+        <v>5.772253402666662</v>
       </c>
       <c r="Q27">
-        <v>42.65850006666666</v>
+        <v>42.47225340266667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08107009252374917</v>
+        <v>0.08145544718617079</v>
       </c>
       <c r="T27">
-        <v>0.7251902247038676</v>
+        <v>0.7331135221560662</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.279700787911382</v>
+        <v>2.192019988376328</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07525511091776638</v>
+        <v>0.07530565244272092</v>
       </c>
       <c r="C28">
-        <v>175.7260203631067</v>
+        <v>172.0596044315625</v>
       </c>
       <c r="D28">
-        <v>253.0240203631067</v>
+        <v>252.5906044315626</v>
       </c>
       <c r="E28">
-        <v>-61.94199999999999</v>
+        <v>-58.70899999999999</v>
       </c>
       <c r="F28">
-        <v>84.05800000000001</v>
+        <v>87.29100000000001</v>
       </c>
       <c r="G28">
         <v>6.76</v>
@@ -3577,28 +3577,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M28">
-        <v>6.371596400000001</v>
+        <v>6.616657800000001</v>
       </c>
       <c r="N28">
-        <v>7.59507026666666</v>
+        <v>7.35000886666666</v>
       </c>
       <c r="O28">
-        <v>1.822816863999998</v>
+        <v>1.764002127999998</v>
       </c>
       <c r="P28">
-        <v>5.772253402666662</v>
+        <v>5.586006738666661</v>
       </c>
       <c r="Q28">
-        <v>42.47225340266667</v>
+        <v>42.28600673866666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08145544718617079</v>
+        <v>0.08185135951057659</v>
       </c>
       <c r="T28">
-        <v>0.7331135221560662</v>
+        <v>0.7412538962507909</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.192019988376328</v>
+        <v>2.110834062880909</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07530565244272092</v>
+        <v>0.07535619396767544</v>
       </c>
       <c r="C29">
-        <v>172.0596044315625</v>
+        <v>168.3946707952115</v>
       </c>
       <c r="D29">
-        <v>252.5906044315626</v>
+        <v>252.1586707952115</v>
       </c>
       <c r="E29">
-        <v>-58.70899999999999</v>
+        <v>-55.47599999999998</v>
       </c>
       <c r="F29">
-        <v>87.29100000000001</v>
+        <v>90.52400000000002</v>
       </c>
       <c r="G29">
         <v>6.76</v>
@@ -3659,28 +3659,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M29">
-        <v>6.616657800000001</v>
+        <v>6.861719200000001</v>
       </c>
       <c r="N29">
-        <v>7.35000886666666</v>
+        <v>7.10494746666666</v>
       </c>
       <c r="O29">
-        <v>1.764002127999998</v>
+        <v>1.705187391999998</v>
       </c>
       <c r="P29">
-        <v>5.586006738666661</v>
+        <v>5.399760074666662</v>
       </c>
       <c r="Q29">
-        <v>42.28600673866666</v>
+        <v>42.09976007466666</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08185135951057659</v>
+        <v>0.08225826939954922</v>
       </c>
       <c r="T29">
-        <v>0.7412538962507909</v>
+        <v>0.7496203918481468</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.110834062880909</v>
+        <v>2.035447132063734</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07535619396767544</v>
+        <v>0.07853641549262996</v>
       </c>
       <c r="C30">
-        <v>168.3946707952115</v>
+        <v>140.6653898035619</v>
       </c>
       <c r="D30">
-        <v>252.1586707952115</v>
+        <v>227.6623898035619</v>
       </c>
       <c r="E30">
-        <v>-55.47599999999998</v>
+        <v>-52.24299999999998</v>
       </c>
       <c r="F30">
-        <v>90.52400000000002</v>
+        <v>93.75700000000002</v>
       </c>
       <c r="G30">
         <v>6.76</v>
@@ -3741,45 +3741,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M30">
-        <v>6.861719200000001</v>
+        <v>8.438130000000001</v>
       </c>
       <c r="N30">
-        <v>7.10494746666666</v>
+        <v>5.52853666666666</v>
       </c>
       <c r="O30">
-        <v>1.705187391999998</v>
+        <v>1.326848799999998</v>
       </c>
       <c r="P30">
-        <v>5.399760074666662</v>
+        <v>4.201687866666662</v>
       </c>
       <c r="Q30">
-        <v>42.09976007466666</v>
+        <v>40.90168786666666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08225826939954922</v>
+        <v>0.08267664153891544</v>
       </c>
       <c r="T30">
-        <v>0.7496203918481468</v>
+        <v>0.7582225633778226</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.035447132063734</v>
+        <v>1.655185054824547</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07853641549262996</v>
+        <v>0.07869487701758447</v>
       </c>
       <c r="C31">
-        <v>140.6653898035619</v>
+        <v>136.3356923012798</v>
       </c>
       <c r="D31">
-        <v>227.6623898035619</v>
+        <v>226.5656923012799</v>
       </c>
       <c r="E31">
-        <v>-52.24300000000001</v>
+        <v>-49.01000000000001</v>
       </c>
       <c r="F31">
-        <v>93.75699999999999</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="G31">
         <v>6.76</v>
@@ -3823,28 +3823,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M31">
-        <v>8.438129999999999</v>
+        <v>8.729099999999999</v>
       </c>
       <c r="N31">
-        <v>5.528536666666662</v>
+        <v>5.237566666666662</v>
       </c>
       <c r="O31">
-        <v>1.326848799999999</v>
+        <v>1.257015999999999</v>
       </c>
       <c r="P31">
-        <v>4.201687866666663</v>
+        <v>3.980550666666663</v>
       </c>
       <c r="Q31">
-        <v>40.90168786666666</v>
+        <v>40.68055066666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08267664153891544</v>
+        <v>0.08310696716797783</v>
       </c>
       <c r="T31">
-        <v>0.7582225633778226</v>
+        <v>0.7670705112369176</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.655185054824548</v>
+        <v>1.60001221966373</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07869487701758447</v>
+        <v>0.07885333854253901</v>
       </c>
       <c r="C32">
-        <v>136.3356923012798</v>
+        <v>132.0165101881406</v>
       </c>
       <c r="D32">
-        <v>226.5656923012799</v>
+        <v>225.4795101881406</v>
       </c>
       <c r="E32">
-        <v>-49.01000000000001</v>
+        <v>-45.777</v>
       </c>
       <c r="F32">
-        <v>96.98999999999999</v>
+        <v>100.223</v>
       </c>
       <c r="G32">
         <v>6.76</v>
@@ -3905,28 +3905,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M32">
-        <v>8.729099999999999</v>
+        <v>9.020069999999999</v>
       </c>
       <c r="N32">
-        <v>5.237566666666662</v>
+        <v>4.946596666666663</v>
       </c>
       <c r="O32">
-        <v>1.257015999999999</v>
+        <v>1.187183199999999</v>
       </c>
       <c r="P32">
-        <v>3.980550666666663</v>
+        <v>3.759413466666664</v>
       </c>
       <c r="Q32">
-        <v>40.68055066666667</v>
+        <v>40.45941346666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08310696716797783</v>
+        <v>0.08354976600367972</v>
       </c>
       <c r="T32">
-        <v>0.7670705112369176</v>
+        <v>0.7761749213527981</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.60001221966373</v>
+        <v>1.548398922255222</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07885333854253901</v>
+        <v>0.07901180006749352</v>
       </c>
       <c r="C33">
-        <v>132.0165101881406</v>
+        <v>127.7076929497556</v>
       </c>
       <c r="D33">
-        <v>225.4795101881406</v>
+        <v>224.4036929497556</v>
       </c>
       <c r="E33">
-        <v>-45.777</v>
+        <v>-42.544</v>
       </c>
       <c r="F33">
-        <v>100.223</v>
+        <v>103.456</v>
       </c>
       <c r="G33">
         <v>6.76</v>
@@ -3987,28 +3987,28 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M33">
-        <v>9.020069999999999</v>
+        <v>9.31104</v>
       </c>
       <c r="N33">
-        <v>4.946596666666663</v>
+        <v>4.655626666666661</v>
       </c>
       <c r="O33">
-        <v>1.187183199999999</v>
+        <v>1.117350399999999</v>
       </c>
       <c r="P33">
-        <v>3.759413466666664</v>
+        <v>3.538276266666663</v>
       </c>
       <c r="Q33">
-        <v>40.45941346666667</v>
+        <v>40.23827626666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08354976600367972</v>
+        <v>0.0840055883345493</v>
       </c>
       <c r="T33">
-        <v>0.7761749213527981</v>
+        <v>0.7855471082367927</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.548398922255222</v>
+        <v>1.500011455934746</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07901180006749352</v>
+        <v>0.09491542864888214</v>
       </c>
       <c r="C34">
-        <v>127.7076929497556</v>
+        <v>51.81253600355707</v>
       </c>
       <c r="D34">
-        <v>224.4036929497556</v>
+        <v>151.7415360035571</v>
       </c>
       <c r="E34">
-        <v>-42.544</v>
+        <v>-39.31099999999999</v>
       </c>
       <c r="F34">
-        <v>103.456</v>
+        <v>106.689</v>
       </c>
       <c r="G34">
         <v>6.76</v>
@@ -4069,45 +4069,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M34">
-        <v>9.31104</v>
+        <v>15.6619452</v>
       </c>
       <c r="N34">
-        <v>4.655626666666661</v>
+        <v>-1.69527853333334</v>
       </c>
       <c r="O34">
-        <v>1.117350399999999</v>
+        <v>-0.4068668480000016</v>
       </c>
       <c r="P34">
-        <v>3.538276266666663</v>
+        <v>-1.288411685333338</v>
       </c>
       <c r="Q34">
-        <v>40.23827626666667</v>
+        <v>35.41158831466667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0840055883345493</v>
+        <v>0.08483508631687031</v>
       </c>
       <c r="T34">
-        <v>0.7855471082367927</v>
+        <v>0.8026024598150662</v>
       </c>
       <c r="U34">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.24</v>
+        <v>0.2140219466481084</v>
       </c>
       <c r="W34">
-        <v>0.0684</v>
+        <v>0.1153815782320577</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.500011455934746</v>
+        <v>0.8917581110337852</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09491542864888214</v>
+        <v>0.09592542864888215</v>
       </c>
       <c r="C35">
-        <v>51.81253600355707</v>
+        <v>45.52202696084858</v>
       </c>
       <c r="D35">
-        <v>151.7415360035571</v>
+        <v>148.6840269608486</v>
       </c>
       <c r="E35">
-        <v>-39.31099999999999</v>
+        <v>-36.07799999999999</v>
       </c>
       <c r="F35">
-        <v>106.689</v>
+        <v>109.922</v>
       </c>
       <c r="G35">
         <v>6.76</v>
@@ -4151,37 +4151,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M35">
-        <v>15.6619452</v>
+        <v>16.1365496</v>
       </c>
       <c r="N35">
-        <v>-1.69527853333334</v>
+        <v>-2.169882933333341</v>
       </c>
       <c r="O35">
-        <v>-0.4068668480000016</v>
+        <v>-0.5207719040000017</v>
       </c>
       <c r="P35">
-        <v>-1.288411685333338</v>
+        <v>-1.649111029333339</v>
       </c>
       <c r="Q35">
-        <v>35.41158831466667</v>
+        <v>35.05088897066666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08483508631687031</v>
+        <v>0.08542652701864108</v>
       </c>
       <c r="T35">
-        <v>0.8026024598150662</v>
+        <v>0.8147631031455975</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2140219466481084</v>
+        <v>0.2077271835113994</v>
       </c>
       <c r="W35">
-        <v>0.1153815782320577</v>
+        <v>0.1163056494605266</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8917581110337852</v>
+        <v>0.8655299312974974</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09592542864888215</v>
+        <v>0.09693542864888215</v>
       </c>
       <c r="C36">
-        <v>45.52202696084858</v>
+        <v>39.3522985281685</v>
       </c>
       <c r="D36">
-        <v>148.6840269608486</v>
+        <v>145.7472985281685</v>
       </c>
       <c r="E36">
-        <v>-36.07799999999999</v>
+        <v>-32.84499999999998</v>
       </c>
       <c r="F36">
-        <v>109.922</v>
+        <v>113.155</v>
       </c>
       <c r="G36">
         <v>6.76</v>
@@ -4233,37 +4233,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M36">
-        <v>16.1365496</v>
+        <v>16.611154</v>
       </c>
       <c r="N36">
-        <v>-2.169882933333341</v>
+        <v>-2.644487333333341</v>
       </c>
       <c r="O36">
-        <v>-0.5207719040000017</v>
+        <v>-0.6346769600000018</v>
       </c>
       <c r="P36">
-        <v>-1.649111029333339</v>
+        <v>-2.009810373333339</v>
       </c>
       <c r="Q36">
-        <v>35.05088897066666</v>
+        <v>34.69018962666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08542652701864108</v>
+        <v>0.08603616589585095</v>
       </c>
       <c r="T36">
-        <v>0.8147631031455975</v>
+        <v>0.8272979201170683</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.2077271835113994</v>
+        <v>0.2017921211253594</v>
       </c>
       <c r="W36">
-        <v>0.1163056494605266</v>
+        <v>0.1171769166187973</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8655299312974974</v>
+        <v>0.8408005046889975</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09693542864888215</v>
+        <v>0.09794542864888214</v>
       </c>
       <c r="C37">
-        <v>39.3522985281685</v>
+        <v>33.29633254001557</v>
       </c>
       <c r="D37">
-        <v>145.7472985281685</v>
+        <v>142.9243325400156</v>
       </c>
       <c r="E37">
-        <v>-32.84499999999998</v>
+        <v>-29.61199999999998</v>
       </c>
       <c r="F37">
-        <v>113.155</v>
+        <v>116.388</v>
       </c>
       <c r="G37">
         <v>6.76</v>
@@ -4315,37 +4315,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M37">
-        <v>16.611154</v>
+        <v>17.0857584</v>
       </c>
       <c r="N37">
-        <v>-2.644487333333341</v>
+        <v>-3.119091733333342</v>
       </c>
       <c r="O37">
-        <v>-0.6346769600000018</v>
+        <v>-0.748582016000002</v>
       </c>
       <c r="P37">
-        <v>-2.009810373333339</v>
+        <v>-2.37050971733334</v>
       </c>
       <c r="Q37">
-        <v>34.69018962666667</v>
+        <v>34.32949028266666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08603616589585095</v>
+        <v>0.0866648559879736</v>
       </c>
       <c r="T37">
-        <v>0.8272979201170683</v>
+        <v>0.8402244501188975</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.2017921211253594</v>
+        <v>0.1961867844274327</v>
       </c>
       <c r="W37">
-        <v>0.1171769166187973</v>
+        <v>0.1179997800460529</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8408005046889975</v>
+        <v>0.8174449351143031</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09794542864888214</v>
+        <v>0.1194699220033586</v>
       </c>
       <c r="C38">
-        <v>33.29633254001558</v>
+        <v>-11.69555307154101</v>
       </c>
       <c r="D38">
-        <v>142.9243325400156</v>
+        <v>101.165446928459</v>
       </c>
       <c r="E38">
-        <v>-29.61199999999999</v>
+        <v>-26.37899999999999</v>
       </c>
       <c r="F38">
-        <v>116.388</v>
+        <v>119.621</v>
       </c>
       <c r="G38">
         <v>6.76</v>
@@ -4397,45 +4397,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M38">
-        <v>17.0857584</v>
+        <v>24.0198968</v>
       </c>
       <c r="N38">
-        <v>-3.119091733333342</v>
+        <v>-10.05323013333334</v>
       </c>
       <c r="O38">
-        <v>-0.748582016000002</v>
+        <v>-2.412775232000001</v>
       </c>
       <c r="P38">
-        <v>-2.37050971733334</v>
+        <v>-7.640454901333339</v>
       </c>
       <c r="Q38">
-        <v>34.32949028266666</v>
+        <v>29.05954509866666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0866648559879736</v>
+        <v>0.0881619066456818</v>
       </c>
       <c r="T38">
-        <v>0.8402244501188975</v>
+        <v>0.8710053873144962</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1961867844274327</v>
+        <v>0.1395509742573081</v>
       </c>
       <c r="W38">
-        <v>0.1179997800460529</v>
+        <v>0.1727781643691325</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8174449351143031</v>
+        <v>0.581462392738784</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1194699220033586</v>
+        <v>0.1210199220033586</v>
       </c>
       <c r="C39">
-        <v>-11.69555307154101</v>
+        <v>-17.01319286593096</v>
       </c>
       <c r="D39">
-        <v>101.165446928459</v>
+        <v>99.08080713406903</v>
       </c>
       <c r="E39">
-        <v>-26.37899999999999</v>
+        <v>-23.146</v>
       </c>
       <c r="F39">
-        <v>119.621</v>
+        <v>122.854</v>
       </c>
       <c r="G39">
         <v>6.76</v>
@@ -4479,37 +4479,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M39">
-        <v>24.0198968</v>
+        <v>24.6690832</v>
       </c>
       <c r="N39">
-        <v>-10.05323013333334</v>
+        <v>-10.70241653333334</v>
       </c>
       <c r="O39">
-        <v>-2.412775232000001</v>
+        <v>-2.568579968000001</v>
       </c>
       <c r="P39">
-        <v>-7.640454901333339</v>
+        <v>-8.133836565333336</v>
       </c>
       <c r="Q39">
-        <v>29.05954509866666</v>
+        <v>28.56616343466667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0881619066456818</v>
+        <v>0.08884516320448313</v>
       </c>
       <c r="T39">
-        <v>0.8710053873144962</v>
+        <v>0.8850538613034397</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1395509742573081</v>
+        <v>0.1358785801979053</v>
       </c>
       <c r="W39">
-        <v>0.1727781643691325</v>
+        <v>0.1735155810962606</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.581462392738784</v>
+        <v>0.5661607508246055</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1210199220033586</v>
+        <v>0.1225699220033586</v>
       </c>
       <c r="C40">
-        <v>-17.01319286593096</v>
+        <v>-22.24665407587059</v>
       </c>
       <c r="D40">
-        <v>99.08080713406903</v>
+        <v>97.0803459241294</v>
       </c>
       <c r="E40">
-        <v>-23.146</v>
+        <v>-19.913</v>
       </c>
       <c r="F40">
-        <v>122.854</v>
+        <v>126.087</v>
       </c>
       <c r="G40">
         <v>6.76</v>
@@ -4561,37 +4561,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M40">
-        <v>24.6690832</v>
+        <v>25.3182696</v>
       </c>
       <c r="N40">
-        <v>-10.70241653333334</v>
+        <v>-11.35160293333334</v>
       </c>
       <c r="O40">
-        <v>-2.568579968000001</v>
+        <v>-2.724384704000001</v>
       </c>
       <c r="P40">
-        <v>-8.133836565333336</v>
+        <v>-8.627218229333337</v>
       </c>
       <c r="Q40">
-        <v>28.56616343466667</v>
+        <v>28.07278177066667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08884516320448313</v>
+        <v>0.08955082161767138</v>
       </c>
       <c r="T40">
-        <v>0.8850538613034397</v>
+        <v>0.8995629409969388</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1358785801979053</v>
+        <v>0.1323945140389847</v>
       </c>
       <c r="W40">
-        <v>0.1735155810962606</v>
+        <v>0.1742151815809719</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5661607508246055</v>
+        <v>0.5516438084957694</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1225699220033586</v>
+        <v>0.1241199220033586</v>
       </c>
       <c r="C41">
-        <v>-22.24665407587059</v>
+        <v>-27.40093454108796</v>
       </c>
       <c r="D41">
-        <v>97.0803459241294</v>
+        <v>95.15906545891205</v>
       </c>
       <c r="E41">
-        <v>-19.913</v>
+        <v>-16.67999999999998</v>
       </c>
       <c r="F41">
-        <v>126.087</v>
+        <v>129.32</v>
       </c>
       <c r="G41">
         <v>6.76</v>
@@ -4643,37 +4643,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M41">
-        <v>25.3182696</v>
+        <v>25.96745600000001</v>
       </c>
       <c r="N41">
-        <v>-11.35160293333334</v>
+        <v>-12.00078933333334</v>
       </c>
       <c r="O41">
-        <v>-2.724384704000001</v>
+        <v>-2.880189440000002</v>
       </c>
       <c r="P41">
-        <v>-8.627218229333337</v>
+        <v>-9.120599893333342</v>
       </c>
       <c r="Q41">
-        <v>28.07278177066667</v>
+        <v>27.57940010666666</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08955082161767138</v>
+        <v>0.0902800019779659</v>
       </c>
       <c r="T41">
-        <v>0.8995629409969388</v>
+        <v>0.9145556566802211</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1323945140389847</v>
+        <v>0.12908465118801</v>
       </c>
       <c r="W41">
-        <v>0.1742151815809719</v>
+        <v>0.1748798020414476</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5516438084957694</v>
+        <v>0.537852713283375</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1241199220033586</v>
+        <v>0.1256699220033586</v>
       </c>
       <c r="C42">
-        <v>-27.40093454108796</v>
+        <v>-32.48064413791356</v>
       </c>
       <c r="D42">
-        <v>95.15906545891205</v>
+        <v>93.31235586208646</v>
       </c>
       <c r="E42">
-        <v>-16.67999999999998</v>
+        <v>-13.44699999999997</v>
       </c>
       <c r="F42">
-        <v>129.32</v>
+        <v>132.553</v>
       </c>
       <c r="G42">
         <v>6.76</v>
@@ -4725,37 +4725,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M42">
-        <v>25.96745600000001</v>
+        <v>26.61664240000001</v>
       </c>
       <c r="N42">
-        <v>-12.00078933333334</v>
+        <v>-12.64997573333335</v>
       </c>
       <c r="O42">
-        <v>-2.880189440000002</v>
+        <v>-3.035994176000003</v>
       </c>
       <c r="P42">
-        <v>-9.120599893333342</v>
+        <v>-9.613981557333343</v>
       </c>
       <c r="Q42">
-        <v>27.57940010666666</v>
+        <v>27.08601844266666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0902800019779659</v>
+        <v>0.09103390031657549</v>
       </c>
       <c r="T42">
-        <v>0.9145556566802211</v>
+        <v>0.9300566000137841</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.12908465118801</v>
+        <v>0.1259362450614732</v>
       </c>
       <c r="W42">
-        <v>0.1748798020414476</v>
+        <v>0.1755120019916562</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.537852713283375</v>
+        <v>0.5247343544228049</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1256699220033586</v>
+        <v>0.1272199220033586</v>
       </c>
       <c r="C43">
-        <v>-32.48064413791356</v>
+        <v>-37.49004170778926</v>
       </c>
       <c r="D43">
-        <v>93.31235586208646</v>
+        <v>91.53595829221076</v>
       </c>
       <c r="E43">
-        <v>-13.44699999999997</v>
+        <v>-10.21399999999997</v>
       </c>
       <c r="F43">
-        <v>132.553</v>
+        <v>135.786</v>
       </c>
       <c r="G43">
         <v>6.76</v>
@@ -4807,37 +4807,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M43">
-        <v>26.61664240000001</v>
+        <v>27.26582880000001</v>
       </c>
       <c r="N43">
-        <v>-12.64997573333335</v>
+        <v>-13.29916213333335</v>
       </c>
       <c r="O43">
-        <v>-3.035994176000003</v>
+        <v>-3.191798912000003</v>
       </c>
       <c r="P43">
-        <v>-9.613981557333343</v>
+        <v>-10.10736322133334</v>
       </c>
       <c r="Q43">
-        <v>27.08601844266666</v>
+        <v>26.59263677866666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09103390031657549</v>
+        <v>0.0918137951496199</v>
       </c>
       <c r="T43">
-        <v>0.9300566000137841</v>
+        <v>0.9460920586347115</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1259362450614732</v>
+        <v>0.1229377630362</v>
       </c>
       <c r="W43">
-        <v>0.1755120019916562</v>
+        <v>0.1761140971823311</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5247343544228049</v>
+        <v>0.5122406793175001</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1272199220033586</v>
+        <v>0.1287699220033586</v>
       </c>
       <c r="C44">
-        <v>-37.49004170778923</v>
+        <v>-42.43306784650467</v>
       </c>
       <c r="D44">
-        <v>91.53595829221076</v>
+        <v>89.82593215349533</v>
       </c>
       <c r="E44">
-        <v>-10.214</v>
+        <v>-6.980999999999995</v>
       </c>
       <c r="F44">
-        <v>135.786</v>
+        <v>139.019</v>
       </c>
       <c r="G44">
         <v>6.76</v>
@@ -4889,37 +4889,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M44">
-        <v>27.2658288</v>
+        <v>27.9150152</v>
       </c>
       <c r="N44">
-        <v>-13.29916213333334</v>
+        <v>-13.94834853333334</v>
       </c>
       <c r="O44">
-        <v>-3.191798912000002</v>
+        <v>-3.347603648000002</v>
       </c>
       <c r="P44">
-        <v>-10.10736322133334</v>
+        <v>-10.60074488533334</v>
       </c>
       <c r="Q44">
-        <v>26.59263677866667</v>
+        <v>26.09925511466666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09181379514961988</v>
+        <v>0.09262105471364832</v>
       </c>
       <c r="T44">
-        <v>0.9460920586347112</v>
+        <v>0.9626901649265484</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1229377630362</v>
+        <v>0.1200787452911721</v>
       </c>
       <c r="W44">
-        <v>0.176114097182331</v>
+        <v>0.1766881879455326</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5122406793175002</v>
+        <v>0.5003281053798838</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1287699220033586</v>
+        <v>0.1459355965278536</v>
       </c>
       <c r="C45">
-        <v>-42.43306784650467</v>
+        <v>-61.06441537397332</v>
       </c>
       <c r="D45">
-        <v>89.82593215349533</v>
+        <v>74.42758462602669</v>
       </c>
       <c r="E45">
-        <v>-6.980999999999995</v>
+        <v>-3.74799999999999</v>
       </c>
       <c r="F45">
-        <v>139.019</v>
+        <v>142.252</v>
       </c>
       <c r="G45">
         <v>6.76</v>
@@ -4971,45 +4971,45 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M45">
-        <v>27.9150152</v>
+        <v>33.5430216</v>
       </c>
       <c r="N45">
-        <v>-13.94834853333334</v>
+        <v>-19.57635493333334</v>
       </c>
       <c r="O45">
-        <v>-3.347603648000002</v>
+        <v>-4.698325184000002</v>
       </c>
       <c r="P45">
-        <v>-10.60074488533334</v>
+        <v>-14.87802974933334</v>
       </c>
       <c r="Q45">
-        <v>26.09925511466666</v>
+        <v>21.82197025066666</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09262105471364832</v>
+        <v>0.09384227805584741</v>
       </c>
       <c r="T45">
-        <v>0.9626901649265484</v>
+        <v>0.9877998022020005</v>
       </c>
       <c r="U45">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1200787452911721</v>
+        <v>0.09993136694638143</v>
       </c>
       <c r="W45">
-        <v>0.1766881879455326</v>
+        <v>0.2122361836740433</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.5003281053798838</v>
+        <v>0.4163806956099226</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1459355965278536</v>
+        <v>0.1478355965278536</v>
       </c>
       <c r="C46">
-        <v>-61.06441537397332</v>
+        <v>-65.68332789471651</v>
       </c>
       <c r="D46">
-        <v>74.42758462602669</v>
+        <v>73.0416721052835</v>
       </c>
       <c r="E46">
-        <v>-3.74799999999999</v>
+        <v>-0.5149999999999864</v>
       </c>
       <c r="F46">
-        <v>142.252</v>
+        <v>145.485</v>
       </c>
       <c r="G46">
         <v>6.76</v>
@@ -5053,37 +5053,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M46">
-        <v>33.5430216</v>
+        <v>34.30536300000001</v>
       </c>
       <c r="N46">
-        <v>-19.57635493333334</v>
+        <v>-20.33869633333335</v>
       </c>
       <c r="O46">
-        <v>-4.698325184000002</v>
+        <v>-4.881287120000002</v>
       </c>
       <c r="P46">
-        <v>-14.87802974933334</v>
+        <v>-15.45740921333334</v>
       </c>
       <c r="Q46">
-        <v>21.82197025066666</v>
+        <v>21.24259078666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09384227805584741</v>
+        <v>0.09471577402049919</v>
       </c>
       <c r="T46">
-        <v>0.9877998022020005</v>
+        <v>1.005759798605673</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.09993136694638143</v>
+        <v>0.0977106699031285</v>
       </c>
       <c r="W46">
-        <v>0.2122361836740433</v>
+        <v>0.2127598240368423</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4163806956099226</v>
+        <v>0.4071277912630354</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1478355965278536</v>
+        <v>0.1497355965278536</v>
       </c>
       <c r="C47">
-        <v>-65.68332789471651</v>
+        <v>-70.2515699257068</v>
       </c>
       <c r="D47">
-        <v>73.0416721052835</v>
+        <v>71.70643007429321</v>
       </c>
       <c r="E47">
-        <v>-0.5149999999999864</v>
+        <v>2.718000000000018</v>
       </c>
       <c r="F47">
-        <v>145.485</v>
+        <v>148.718</v>
       </c>
       <c r="G47">
         <v>6.76</v>
@@ -5135,37 +5135,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M47">
-        <v>34.30536300000001</v>
+        <v>35.0677044</v>
       </c>
       <c r="N47">
-        <v>-20.33869633333335</v>
+        <v>-21.10103773333334</v>
       </c>
       <c r="O47">
-        <v>-4.881287120000002</v>
+        <v>-5.064249056000002</v>
       </c>
       <c r="P47">
-        <v>-15.45740921333334</v>
+        <v>-16.03678867733334</v>
       </c>
       <c r="Q47">
-        <v>21.24259078666666</v>
+        <v>20.66321132266666</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09471577402049919</v>
+        <v>0.09562162168754545</v>
       </c>
       <c r="T47">
-        <v>1.005759798605673</v>
+        <v>1.024384980061334</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0977106699031285</v>
+        <v>0.09558652490523441</v>
       </c>
       <c r="W47">
-        <v>0.2127598240368423</v>
+        <v>0.2132606974273457</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4071277912630354</v>
+        <v>0.3982771871051434</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1497355965278536</v>
+        <v>0.1516355965278536</v>
       </c>
       <c r="C48">
-        <v>-70.2515699257068</v>
+        <v>-74.77187043338904</v>
       </c>
       <c r="D48">
-        <v>71.70643007429321</v>
+        <v>70.41912956661098</v>
       </c>
       <c r="E48">
-        <v>2.718000000000018</v>
+        <v>5.951000000000022</v>
       </c>
       <c r="F48">
-        <v>148.718</v>
+        <v>151.951</v>
       </c>
       <c r="G48">
         <v>6.76</v>
@@ -5217,37 +5217,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M48">
-        <v>35.0677044</v>
+        <v>35.83004580000001</v>
       </c>
       <c r="N48">
-        <v>-21.10103773333334</v>
+        <v>-21.86337913333335</v>
       </c>
       <c r="O48">
-        <v>-5.064249056000002</v>
+        <v>-5.247210992000003</v>
       </c>
       <c r="P48">
-        <v>-16.03678867733334</v>
+        <v>-16.61616814133334</v>
       </c>
       <c r="Q48">
-        <v>20.66321132266666</v>
+        <v>20.08383185866666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09562162168754545</v>
+        <v>0.09656165228542368</v>
       </c>
       <c r="T48">
-        <v>1.024384980061334</v>
+        <v>1.043712998553057</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.09558652490523441</v>
+        <v>0.09355276905618685</v>
       </c>
       <c r="W48">
-        <v>0.2132606974273457</v>
+        <v>0.2137402570565512</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3982771871051434</v>
+        <v>0.3898032044007785</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1516355965278536</v>
+        <v>0.1535355965278536</v>
       </c>
       <c r="C49">
-        <v>-74.77187043338904</v>
+        <v>-79.24676587453017</v>
       </c>
       <c r="D49">
-        <v>70.41912956661098</v>
+        <v>69.17723412546985</v>
       </c>
       <c r="E49">
-        <v>5.951000000000022</v>
+        <v>9.184000000000026</v>
       </c>
       <c r="F49">
-        <v>151.951</v>
+        <v>155.184</v>
       </c>
       <c r="G49">
         <v>6.76</v>
@@ -5299,37 +5299,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M49">
-        <v>35.83004580000001</v>
+        <v>36.5923872</v>
       </c>
       <c r="N49">
-        <v>-21.86337913333335</v>
+        <v>-22.62572053333334</v>
       </c>
       <c r="O49">
-        <v>-5.247210992000003</v>
+        <v>-5.430172928000002</v>
       </c>
       <c r="P49">
-        <v>-16.61616814133334</v>
+        <v>-17.19554760533334</v>
       </c>
       <c r="Q49">
-        <v>20.08383185866666</v>
+        <v>19.50445239466666</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09656165228542368</v>
+        <v>0.09753783790629721</v>
       </c>
       <c r="T49">
-        <v>1.043712998553057</v>
+        <v>1.063784402371385</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.09355276905618685</v>
+        <v>0.09160375303418297</v>
       </c>
       <c r="W49">
-        <v>0.2137402570565512</v>
+        <v>0.2141998350345397</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3898032044007785</v>
+        <v>0.3816823043090958</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1535355965278536</v>
+        <v>0.1554355965278536</v>
       </c>
       <c r="C50">
-        <v>-79.24676587453014</v>
+        <v>-83.67861687731552</v>
       </c>
       <c r="D50">
-        <v>69.17723412546985</v>
+        <v>67.97838312268448</v>
       </c>
       <c r="E50">
-        <v>9.183999999999997</v>
+        <v>12.417</v>
       </c>
       <c r="F50">
-        <v>155.184</v>
+        <v>158.417</v>
       </c>
       <c r="G50">
         <v>6.76</v>
@@ -5381,37 +5381,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M50">
-        <v>36.5923872</v>
+        <v>37.3547286</v>
       </c>
       <c r="N50">
-        <v>-22.62572053333334</v>
+        <v>-23.38806193333334</v>
       </c>
       <c r="O50">
-        <v>-5.430172928</v>
+        <v>-5.613134864000001</v>
       </c>
       <c r="P50">
-        <v>-17.19554760533333</v>
+        <v>-17.77492706933334</v>
       </c>
       <c r="Q50">
-        <v>19.50445239466667</v>
+        <v>18.92507293066667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09753783790629721</v>
+        <v>0.09855230531622461</v>
       </c>
       <c r="T50">
-        <v>1.063784402371385</v>
+        <v>1.084642920064942</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.091603753034183</v>
+        <v>0.08973428868654661</v>
       </c>
       <c r="W50">
-        <v>0.2141998350345397</v>
+        <v>0.2146406547277123</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3816823043090958</v>
+        <v>0.3738928695272775</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1554355965278536</v>
+        <v>0.1573355965278536</v>
       </c>
       <c r="C51">
-        <v>-83.67861687731552</v>
+        <v>-88.06962321747839</v>
       </c>
       <c r="D51">
-        <v>67.97838312268448</v>
+        <v>66.82037678252161</v>
       </c>
       <c r="E51">
-        <v>12.417</v>
+        <v>15.65000000000001</v>
       </c>
       <c r="F51">
-        <v>158.417</v>
+        <v>161.65</v>
       </c>
       <c r="G51">
         <v>6.76</v>
@@ -5463,37 +5463,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M51">
-        <v>37.3547286</v>
+        <v>38.11707000000001</v>
       </c>
       <c r="N51">
-        <v>-23.38806193333334</v>
+        <v>-24.15040333333334</v>
       </c>
       <c r="O51">
-        <v>-5.613134864000001</v>
+        <v>-5.796096800000003</v>
       </c>
       <c r="P51">
-        <v>-17.77492706933334</v>
+        <v>-18.35430653333334</v>
       </c>
       <c r="Q51">
-        <v>18.92507293066667</v>
+        <v>18.34569346666666</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09855230531622461</v>
+        <v>0.09960735142254909</v>
       </c>
       <c r="T51">
-        <v>1.084642920064942</v>
+        <v>1.10633577846624</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08973428868654661</v>
+        <v>0.08793960291281565</v>
       </c>
       <c r="W51">
-        <v>0.2146406547277123</v>
+        <v>0.2150638416331581</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3738928695272775</v>
+        <v>0.3664150121367319</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1573355965278536</v>
+        <v>0.1592355965278536</v>
       </c>
       <c r="C52">
-        <v>-88.06962321747839</v>
+        <v>-92.42183728936469</v>
       </c>
       <c r="D52">
-        <v>66.82037678252161</v>
+        <v>65.70116271063532</v>
       </c>
       <c r="E52">
-        <v>15.65000000000001</v>
+        <v>18.88300000000001</v>
       </c>
       <c r="F52">
-        <v>161.65</v>
+        <v>164.883</v>
       </c>
       <c r="G52">
         <v>6.76</v>
@@ -5545,37 +5545,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M52">
-        <v>38.11707000000001</v>
+        <v>38.8794114</v>
       </c>
       <c r="N52">
-        <v>-24.15040333333334</v>
+        <v>-24.91274473333334</v>
       </c>
       <c r="O52">
-        <v>-5.796096800000003</v>
+        <v>-5.979058736000002</v>
       </c>
       <c r="P52">
-        <v>-18.35430653333334</v>
+        <v>-18.93368599733334</v>
       </c>
       <c r="Q52">
-        <v>18.34569346666666</v>
+        <v>17.76631400266666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09960735142254909</v>
+        <v>0.1007054606352542</v>
       </c>
       <c r="T52">
-        <v>1.10633577846624</v>
+        <v>1.128914059659429</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08793960291281565</v>
+        <v>0.08621529697334869</v>
       </c>
       <c r="W52">
-        <v>0.2150638416331581</v>
+        <v>0.2154704329736844</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3664150121367319</v>
+        <v>0.3592304040556196</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1592355965278536</v>
+        <v>0.1611355965278536</v>
       </c>
       <c r="C53">
-        <v>-92.42183728936469</v>
+        <v>-96.7371762454914</v>
       </c>
       <c r="D53">
-        <v>65.70116271063532</v>
+        <v>64.61882375450861</v>
       </c>
       <c r="E53">
-        <v>18.88300000000001</v>
+        <v>22.11600000000001</v>
       </c>
       <c r="F53">
-        <v>164.883</v>
+        <v>168.116</v>
       </c>
       <c r="G53">
         <v>6.76</v>
@@ -5627,37 +5627,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M53">
-        <v>38.8794114</v>
+        <v>39.64175280000001</v>
       </c>
       <c r="N53">
-        <v>-24.91274473333334</v>
+        <v>-25.67508613333334</v>
       </c>
       <c r="O53">
-        <v>-5.979058736000002</v>
+        <v>-6.162020672000002</v>
       </c>
       <c r="P53">
-        <v>-18.93368599733334</v>
+        <v>-19.51306546133334</v>
       </c>
       <c r="Q53">
-        <v>17.76631400266666</v>
+        <v>17.18693453866666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1007054606352542</v>
+        <v>0.1018493243984886</v>
       </c>
       <c r="T53">
-        <v>1.128914059659429</v>
+        <v>1.152433102569</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08621529697334869</v>
+        <v>0.08455731049309198</v>
       </c>
       <c r="W53">
-        <v>0.2154704329736844</v>
+        <v>0.2158613861857289</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3592304040556196</v>
+        <v>0.3523221270545499</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1611355965278536</v>
+        <v>0.1630355965278536</v>
       </c>
       <c r="C54">
-        <v>-96.7371762454914</v>
+        <v>-101.0174329556528</v>
       </c>
       <c r="D54">
-        <v>64.61882375450861</v>
+        <v>63.57156704434723</v>
       </c>
       <c r="E54">
-        <v>22.11600000000001</v>
+        <v>25.34900000000002</v>
       </c>
       <c r="F54">
-        <v>168.116</v>
+        <v>171.349</v>
       </c>
       <c r="G54">
         <v>6.76</v>
@@ -5709,37 +5709,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M54">
-        <v>39.64175280000001</v>
+        <v>40.4040942</v>
       </c>
       <c r="N54">
-        <v>-25.67508613333334</v>
+        <v>-26.43742753333334</v>
       </c>
       <c r="O54">
-        <v>-6.162020672000002</v>
+        <v>-6.344982608000001</v>
       </c>
       <c r="P54">
-        <v>-19.51306546133334</v>
+        <v>-20.09244492533334</v>
       </c>
       <c r="Q54">
-        <v>17.18693453866666</v>
+        <v>16.60755507466666</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1018493243984886</v>
+        <v>0.1030418632154778</v>
       </c>
       <c r="T54">
-        <v>1.152433102569</v>
+        <v>1.17695295581515</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08455731049309198</v>
+        <v>0.08296188954039213</v>
       </c>
       <c r="W54">
-        <v>0.2158613861857289</v>
+        <v>0.2162375864463756</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3523221270545499</v>
+        <v>0.3456745397516339</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1630355965278536</v>
+        <v>0.1649355965278536</v>
       </c>
       <c r="C55">
-        <v>-101.0174329556528</v>
+        <v>-105.2642859173579</v>
       </c>
       <c r="D55">
-        <v>63.57156704434723</v>
+        <v>62.55771408264217</v>
       </c>
       <c r="E55">
-        <v>25.34900000000002</v>
+        <v>28.58200000000002</v>
       </c>
       <c r="F55">
-        <v>171.349</v>
+        <v>174.582</v>
       </c>
       <c r="G55">
         <v>6.76</v>
@@ -5791,37 +5791,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M55">
-        <v>40.4040942</v>
+        <v>41.16643560000001</v>
       </c>
       <c r="N55">
-        <v>-26.43742753333334</v>
+        <v>-27.19976893333335</v>
       </c>
       <c r="O55">
-        <v>-6.344982608000001</v>
+        <v>-6.527944544000003</v>
       </c>
       <c r="P55">
-        <v>-20.09244492533334</v>
+        <v>-20.67182438933334</v>
       </c>
       <c r="Q55">
-        <v>16.60755507466666</v>
+        <v>16.02817561066666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1030418632154778</v>
+        <v>0.104286251546249</v>
       </c>
       <c r="T55">
-        <v>1.17695295581515</v>
+        <v>1.202538889637218</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.08296188954039213</v>
+        <v>0.0814255582526071</v>
       </c>
       <c r="W55">
-        <v>0.2162375864463756</v>
+        <v>0.2165998533640353</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3456745397516339</v>
+        <v>0.3392731593858629</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1649355965278536</v>
+        <v>0.1668355965278536</v>
       </c>
       <c r="C56">
-        <v>-105.2642859173579</v>
+        <v>-109.4793082328315</v>
       </c>
       <c r="D56">
-        <v>62.55771408264217</v>
+        <v>61.57569176716851</v>
       </c>
       <c r="E56">
-        <v>28.58200000000002</v>
+        <v>31.81500000000003</v>
       </c>
       <c r="F56">
-        <v>174.582</v>
+        <v>177.815</v>
       </c>
       <c r="G56">
         <v>6.76</v>
@@ -5873,37 +5873,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M56">
-        <v>41.16643560000001</v>
+        <v>41.92877700000001</v>
       </c>
       <c r="N56">
-        <v>-27.19976893333335</v>
+        <v>-27.96211033333335</v>
       </c>
       <c r="O56">
-        <v>-6.527944544000003</v>
+        <v>-6.710906480000004</v>
       </c>
       <c r="P56">
-        <v>-20.67182438933334</v>
+        <v>-21.25120385333334</v>
       </c>
       <c r="Q56">
-        <v>16.02817561066666</v>
+        <v>15.44879614666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.104286251546249</v>
+        <v>0.1055859460250546</v>
       </c>
       <c r="T56">
-        <v>1.202538889637218</v>
+        <v>1.229261976073601</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0814255582526071</v>
+        <v>0.07994509355710513</v>
       </c>
       <c r="W56">
-        <v>0.2165998533640353</v>
+        <v>0.2169489469392346</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3392731593858629</v>
+        <v>0.333104556487938</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1668355965278536</v>
+        <v>0.1687355965278536</v>
       </c>
       <c r="C57">
-        <v>-109.4793082328315</v>
+        <v>-113.6639757535655</v>
       </c>
       <c r="D57">
-        <v>61.57569176716851</v>
+        <v>60.62402424643449</v>
       </c>
       <c r="E57">
-        <v>31.81500000000003</v>
+        <v>35.04800000000003</v>
       </c>
       <c r="F57">
-        <v>177.815</v>
+        <v>181.048</v>
       </c>
       <c r="G57">
         <v>6.76</v>
@@ -5955,37 +5955,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M57">
-        <v>41.92877700000001</v>
+        <v>42.69111840000001</v>
       </c>
       <c r="N57">
-        <v>-27.96211033333335</v>
+        <v>-28.72445173333335</v>
       </c>
       <c r="O57">
-        <v>-6.710906480000004</v>
+        <v>-6.893868416000003</v>
       </c>
       <c r="P57">
-        <v>-21.25120385333334</v>
+        <v>-21.83058331733334</v>
       </c>
       <c r="Q57">
-        <v>15.44879614666666</v>
+        <v>14.86941668266666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1055859460250546</v>
+        <v>0.106944717525624</v>
       </c>
       <c r="T57">
-        <v>1.229261976073601</v>
+        <v>1.257199748257092</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07994509355710513</v>
+        <v>0.07851750260072825</v>
       </c>
       <c r="W57">
-        <v>0.2169489469392346</v>
+        <v>0.2172855728867483</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.333104556487938</v>
+        <v>0.3271562608363677</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1687355965278536</v>
+        <v>0.1706355965278536</v>
       </c>
       <c r="C58">
-        <v>-113.6639757535655</v>
+        <v>-117.8196744811078</v>
       </c>
       <c r="D58">
-        <v>60.62402424643449</v>
+        <v>59.70132551889224</v>
       </c>
       <c r="E58">
-        <v>35.04800000000003</v>
+        <v>38.28100000000003</v>
       </c>
       <c r="F58">
-        <v>181.048</v>
+        <v>184.281</v>
       </c>
       <c r="G58">
         <v>6.76</v>
@@ -6037,37 +6037,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M58">
-        <v>42.69111840000001</v>
+        <v>43.45345980000001</v>
       </c>
       <c r="N58">
-        <v>-28.72445173333335</v>
+        <v>-29.48679313333335</v>
       </c>
       <c r="O58">
-        <v>-6.893868416000003</v>
+        <v>-7.076830352000004</v>
       </c>
       <c r="P58">
-        <v>-21.83058331733334</v>
+        <v>-22.40996278133335</v>
       </c>
       <c r="Q58">
-        <v>14.86941668266666</v>
+        <v>14.29003721866665</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.106944717525624</v>
+        <v>0.1083666877006385</v>
       </c>
       <c r="T58">
-        <v>1.257199748257092</v>
+        <v>1.286436951704931</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07851750260072825</v>
+        <v>0.07714000255510144</v>
       </c>
       <c r="W58">
-        <v>0.2172855728867483</v>
+        <v>0.2176103873975071</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3271562608363677</v>
+        <v>0.3214166773129227</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1706355965278536</v>
+        <v>0.1725355965278536</v>
       </c>
       <c r="C59">
-        <v>-117.8196744811078</v>
+        <v>-121.9477073021429</v>
       </c>
       <c r="D59">
-        <v>59.70132551889224</v>
+        <v>58.80629269785715</v>
       </c>
       <c r="E59">
-        <v>38.28100000000003</v>
+        <v>41.51400000000004</v>
       </c>
       <c r="F59">
-        <v>184.281</v>
+        <v>187.514</v>
       </c>
       <c r="G59">
         <v>6.76</v>
@@ -6119,37 +6119,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M59">
-        <v>43.45345980000001</v>
+        <v>44.21580120000001</v>
       </c>
       <c r="N59">
-        <v>-29.48679313333335</v>
+        <v>-30.24913453333335</v>
       </c>
       <c r="O59">
-        <v>-7.076830352000004</v>
+        <v>-7.259792288000003</v>
       </c>
       <c r="P59">
-        <v>-22.40996278133335</v>
+        <v>-22.98934224533334</v>
       </c>
       <c r="Q59">
-        <v>14.29003721866665</v>
+        <v>13.71065775466666</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1083666877006385</v>
+        <v>0.1098563707411299</v>
       </c>
       <c r="T59">
-        <v>1.286436951704931</v>
+        <v>1.317066402936001</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07714000255510144</v>
+        <v>0.07581000251104797</v>
       </c>
       <c r="W59">
-        <v>0.2176103873975071</v>
+        <v>0.2179240014078949</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3214166773129227</v>
+        <v>0.3158750104626999</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1725355965278536</v>
+        <v>0.1744355965278536</v>
       </c>
       <c r="C60">
-        <v>-121.9477073021428</v>
+        <v>-126.0493001266938</v>
       </c>
       <c r="D60">
-        <v>58.80629269785715</v>
+        <v>57.93769987330615</v>
       </c>
       <c r="E60">
-        <v>41.51399999999998</v>
+        <v>44.74699999999999</v>
       </c>
       <c r="F60">
-        <v>187.514</v>
+        <v>190.747</v>
       </c>
       <c r="G60">
         <v>6.76</v>
@@ -6201,37 +6201,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M60">
-        <v>44.21580119999999</v>
+        <v>44.9781426</v>
       </c>
       <c r="N60">
-        <v>-30.24913453333333</v>
+        <v>-31.01147593333334</v>
       </c>
       <c r="O60">
-        <v>-7.259792288</v>
+        <v>-7.442754224000001</v>
       </c>
       <c r="P60">
-        <v>-22.98934224533333</v>
+        <v>-23.56872170933334</v>
       </c>
       <c r="Q60">
-        <v>13.71065775466667</v>
+        <v>13.13127829066667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1098563707411299</v>
+        <v>0.1114187212470111</v>
       </c>
       <c r="T60">
-        <v>1.317066402936</v>
+        <v>1.349189973739317</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.075810002511048</v>
+        <v>0.07452508721425057</v>
       </c>
       <c r="W60">
-        <v>0.2179240014078949</v>
+        <v>0.2182269844348797</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3158750104627001</v>
+        <v>0.3105211967260441</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1744355965278536</v>
+        <v>0.1763355965278536</v>
       </c>
       <c r="C61">
-        <v>-126.0493001266938</v>
+        <v>-130.1256074902588</v>
       </c>
       <c r="D61">
-        <v>57.93769987330615</v>
+        <v>57.0943925097412</v>
       </c>
       <c r="E61">
-        <v>44.74699999999999</v>
+        <v>47.97999999999999</v>
       </c>
       <c r="F61">
-        <v>190.747</v>
+        <v>193.98</v>
       </c>
       <c r="G61">
         <v>6.76</v>
@@ -6283,37 +6283,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M61">
-        <v>44.9781426</v>
+        <v>45.740484</v>
       </c>
       <c r="N61">
-        <v>-31.01147593333334</v>
+        <v>-31.77381733333334</v>
       </c>
       <c r="O61">
-        <v>-7.442754224000001</v>
+        <v>-7.625716160000001</v>
       </c>
       <c r="P61">
-        <v>-23.56872170933334</v>
+        <v>-24.14810117333334</v>
       </c>
       <c r="Q61">
-        <v>13.13127829066667</v>
+        <v>12.55189882666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1114187212470111</v>
+        <v>0.1130591892781864</v>
       </c>
       <c r="T61">
-        <v>1.349189973739317</v>
+        <v>1.3829197230828</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07452508721425057</v>
+        <v>0.07328300242734638</v>
       </c>
       <c r="W61">
-        <v>0.2182269844348797</v>
+        <v>0.2185198680276317</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3105211967260441</v>
+        <v>0.3053458434472767</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1763355965278536</v>
+        <v>0.1782355965278536</v>
       </c>
       <c r="C62">
-        <v>-130.1256074902588</v>
+        <v>-134.1777176737184</v>
       </c>
       <c r="D62">
-        <v>57.0943925097412</v>
+        <v>56.27528232628163</v>
       </c>
       <c r="E62">
-        <v>47.97999999999999</v>
+        <v>51.21299999999999</v>
       </c>
       <c r="F62">
-        <v>193.98</v>
+        <v>197.213</v>
       </c>
       <c r="G62">
         <v>6.76</v>
@@ -6365,37 +6365,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M62">
-        <v>45.740484</v>
+        <v>46.5028254</v>
       </c>
       <c r="N62">
-        <v>-31.77381733333334</v>
+        <v>-32.53615873333334</v>
       </c>
       <c r="O62">
-        <v>-7.625716160000001</v>
+        <v>-7.808678096</v>
       </c>
       <c r="P62">
-        <v>-24.14810117333334</v>
+        <v>-24.72748063733334</v>
       </c>
       <c r="Q62">
-        <v>12.55189882666667</v>
+        <v>11.97251936266667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1130591892781864</v>
+        <v>0.1147837838750629</v>
       </c>
       <c r="T62">
-        <v>1.3829197230828</v>
+        <v>1.418379203161847</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07328300242734638</v>
+        <v>0.07208164173181612</v>
       </c>
       <c r="W62">
-        <v>0.2185198680276317</v>
+        <v>0.2188031488796378</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3053458434472767</v>
+        <v>0.3003401738825672</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1782355965278536</v>
+        <v>0.1801355965278536</v>
       </c>
       <c r="C63">
-        <v>-134.1777176737184</v>
+        <v>-138.2066573887571</v>
       </c>
       <c r="D63">
-        <v>56.27528232628163</v>
+        <v>55.47934261124293</v>
       </c>
       <c r="E63">
-        <v>51.21299999999999</v>
+        <v>54.446</v>
       </c>
       <c r="F63">
-        <v>197.213</v>
+        <v>200.446</v>
       </c>
       <c r="G63">
         <v>6.76</v>
@@ -6447,37 +6447,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M63">
-        <v>46.5028254</v>
+        <v>47.2651668</v>
       </c>
       <c r="N63">
-        <v>-32.53615873333334</v>
+        <v>-33.29850013333334</v>
       </c>
       <c r="O63">
-        <v>-7.808678096</v>
+        <v>-7.991640032000002</v>
       </c>
       <c r="P63">
-        <v>-24.72748063733334</v>
+        <v>-25.30686010133334</v>
       </c>
       <c r="Q63">
-        <v>11.97251936266667</v>
+        <v>11.39313989866666</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1147837838750629</v>
+        <v>0.1165991466086172</v>
       </c>
       <c r="T63">
-        <v>1.418379203161847</v>
+        <v>1.455704971666106</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07208164173181612</v>
+        <v>0.07091903460710941</v>
       </c>
       <c r="W63">
-        <v>0.2188031488796378</v>
+        <v>0.2190772916396436</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3003401738825672</v>
+        <v>0.2954959775296225</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1801355965278536</v>
+        <v>0.1820355965278536</v>
       </c>
       <c r="C64">
-        <v>-138.2066573887571</v>
+        <v>-142.2133960712152</v>
       </c>
       <c r="D64">
-        <v>55.47934261124293</v>
+        <v>54.70560392878478</v>
       </c>
       <c r="E64">
-        <v>54.446</v>
+        <v>57.679</v>
       </c>
       <c r="F64">
-        <v>200.446</v>
+        <v>203.679</v>
       </c>
       <c r="G64">
         <v>6.76</v>
@@ -6529,37 +6529,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M64">
-        <v>47.2651668</v>
+        <v>48.0275082</v>
       </c>
       <c r="N64">
-        <v>-33.29850013333334</v>
+        <v>-34.06084153333334</v>
       </c>
       <c r="O64">
-        <v>-7.991640032000002</v>
+        <v>-8.174601968000001</v>
       </c>
       <c r="P64">
-        <v>-25.30686010133334</v>
+        <v>-25.88623956533334</v>
       </c>
       <c r="Q64">
-        <v>11.39313989866666</v>
+        <v>10.81376043466667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1165991466086172</v>
+        <v>0.1185126370574988</v>
       </c>
       <c r="T64">
-        <v>1.455704971666106</v>
+        <v>1.495048349278703</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07091903460710941</v>
+        <v>0.06979333564509181</v>
       </c>
       <c r="W64">
-        <v>0.2190772916396436</v>
+        <v>0.2193427314548874</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2954959775296225</v>
+        <v>0.2908055651878825</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1820355965278536</v>
+        <v>0.1839355965278536</v>
       </c>
       <c r="C65">
-        <v>-142.2133960712152</v>
+        <v>-146.1988498201208</v>
       </c>
       <c r="D65">
-        <v>54.70560392878478</v>
+        <v>53.95315017987921</v>
       </c>
       <c r="E65">
-        <v>57.679</v>
+        <v>60.91200000000001</v>
       </c>
       <c r="F65">
-        <v>203.679</v>
+        <v>206.912</v>
       </c>
       <c r="G65">
         <v>6.76</v>
@@ -6611,37 +6611,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M65">
-        <v>48.0275082</v>
+        <v>48.7898496</v>
       </c>
       <c r="N65">
-        <v>-34.06084153333334</v>
+        <v>-34.82318293333334</v>
       </c>
       <c r="O65">
-        <v>-8.174601968000001</v>
+        <v>-8.357563904000003</v>
       </c>
       <c r="P65">
-        <v>-25.88623956533334</v>
+        <v>-26.46561902933334</v>
       </c>
       <c r="Q65">
-        <v>10.81376043466667</v>
+        <v>10.23438097066666</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1185126370574988</v>
+        <v>0.1205324325313182</v>
       </c>
       <c r="T65">
-        <v>1.495048349278703</v>
+        <v>1.536577470092001</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06979333564509181</v>
+        <v>0.06870281477563724</v>
       </c>
       <c r="W65">
-        <v>0.2193427314548874</v>
+        <v>0.2195998762759047</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2908055651878825</v>
+        <v>0.2862617282318218</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1839355965278536</v>
+        <v>0.1858355965278536</v>
       </c>
       <c r="C66">
-        <v>-146.1988498201208</v>
+        <v>-150.1638850160531</v>
       </c>
       <c r="D66">
-        <v>53.95315017987921</v>
+        <v>53.22111498394685</v>
       </c>
       <c r="E66">
-        <v>60.91200000000001</v>
+        <v>64.14500000000001</v>
       </c>
       <c r="F66">
-        <v>206.912</v>
+        <v>210.145</v>
       </c>
       <c r="G66">
         <v>6.76</v>
@@ -6693,37 +6693,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M66">
-        <v>48.7898496</v>
+        <v>49.55219100000001</v>
       </c>
       <c r="N66">
-        <v>-34.82318293333334</v>
+        <v>-35.58552433333335</v>
       </c>
       <c r="O66">
-        <v>-8.357563904000003</v>
+        <v>-8.540525840000003</v>
       </c>
       <c r="P66">
-        <v>-26.46561902933334</v>
+        <v>-27.04499849333335</v>
       </c>
       <c r="Q66">
-        <v>10.23438097066666</v>
+        <v>9.655001506666657</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1205324325313182</v>
+        <v>0.1226676448893559</v>
       </c>
       <c r="T66">
-        <v>1.536577470092001</v>
+        <v>1.580479683523201</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06870281477563724</v>
+        <v>0.06764584839447359</v>
       </c>
       <c r="W66">
-        <v>0.2195998762759047</v>
+        <v>0.2198491089485831</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2862617282318218</v>
+        <v>0.2818577016436399</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1858355965278536</v>
+        <v>0.1877355965278536</v>
       </c>
       <c r="C67">
-        <v>-150.1638850160531</v>
+        <v>-154.1093216488865</v>
       </c>
       <c r="D67">
-        <v>53.22111498394685</v>
+        <v>52.5086783511135</v>
       </c>
       <c r="E67">
-        <v>64.14500000000001</v>
+        <v>67.37800000000001</v>
       </c>
       <c r="F67">
-        <v>210.145</v>
+        <v>213.378</v>
       </c>
       <c r="G67">
         <v>6.76</v>
@@ -6775,37 +6775,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M67">
-        <v>49.55219100000001</v>
+        <v>50.3145324</v>
       </c>
       <c r="N67">
-        <v>-35.58552433333335</v>
+        <v>-36.34786573333334</v>
       </c>
       <c r="O67">
-        <v>-8.540525840000003</v>
+        <v>-8.723487776000002</v>
       </c>
       <c r="P67">
-        <v>-27.04499849333335</v>
+        <v>-27.62437795733334</v>
       </c>
       <c r="Q67">
-        <v>9.655001506666657</v>
+        <v>9.075622042666662</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1226676448893559</v>
+        <v>0.1249284579743369</v>
       </c>
       <c r="T67">
-        <v>1.580479683523201</v>
+        <v>1.626964380097413</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06764584839447359</v>
+        <v>0.06662091129758763</v>
       </c>
       <c r="W67">
-        <v>0.2198491089485831</v>
+        <v>0.2200907891160288</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2818577016436399</v>
+        <v>0.2775871304066151</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1877355965278536</v>
+        <v>0.1896355965278536</v>
       </c>
       <c r="C68">
-        <v>-154.1093216488865</v>
+        <v>-158.0359363817861</v>
       </c>
       <c r="D68">
-        <v>52.5086783511135</v>
+        <v>51.81506361821393</v>
       </c>
       <c r="E68">
-        <v>67.37800000000001</v>
+        <v>70.61100000000002</v>
       </c>
       <c r="F68">
-        <v>213.378</v>
+        <v>216.611</v>
       </c>
       <c r="G68">
         <v>6.76</v>
@@ -6857,37 +6857,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M68">
-        <v>50.3145324</v>
+        <v>51.07687380000001</v>
       </c>
       <c r="N68">
-        <v>-36.34786573333334</v>
+        <v>-37.11020713333335</v>
       </c>
       <c r="O68">
-        <v>-8.723487776000002</v>
+        <v>-8.906449712000002</v>
       </c>
       <c r="P68">
-        <v>-27.62437795733334</v>
+        <v>-28.20375742133334</v>
       </c>
       <c r="Q68">
-        <v>9.075622042666662</v>
+        <v>8.49624257866666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1249284579743369</v>
+        <v>0.1273262900341653</v>
       </c>
       <c r="T68">
-        <v>1.626964380097413</v>
+        <v>1.676266331009455</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06662091129758763</v>
+        <v>0.06562656933792213</v>
       </c>
       <c r="W68">
-        <v>0.2200907891160288</v>
+        <v>0.220325254950118</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2775871304066151</v>
+        <v>0.2734440389080088</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1896355965278536</v>
+        <v>0.1915355965278536</v>
       </c>
       <c r="C69">
-        <v>-158.0359363817861</v>
+        <v>-161.9444653755264</v>
       </c>
       <c r="D69">
-        <v>51.81506361821393</v>
+        <v>51.13953462447363</v>
       </c>
       <c r="E69">
-        <v>70.61100000000002</v>
+        <v>73.84400000000002</v>
       </c>
       <c r="F69">
-        <v>216.611</v>
+        <v>219.844</v>
       </c>
       <c r="G69">
         <v>6.76</v>
@@ -6939,37 +6939,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M69">
-        <v>51.07687380000001</v>
+        <v>51.83921520000001</v>
       </c>
       <c r="N69">
-        <v>-37.11020713333335</v>
+        <v>-37.87254853333334</v>
       </c>
       <c r="O69">
-        <v>-8.906449712000002</v>
+        <v>-9.089411648000002</v>
       </c>
       <c r="P69">
-        <v>-28.20375742133334</v>
+        <v>-28.78313688533334</v>
       </c>
       <c r="Q69">
-        <v>8.49624257866666</v>
+        <v>7.916863114666661</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1273262900341653</v>
+        <v>0.129873986597733</v>
       </c>
       <c r="T69">
-        <v>1.676266331009455</v>
+        <v>1.728649653853501</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06562656933792213</v>
+        <v>0.06466147273001151</v>
       </c>
       <c r="W69">
-        <v>0.220325254950118</v>
+        <v>0.2205528247302633</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2734440389080088</v>
+        <v>0.2694228030417146</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1915355965278536</v>
+        <v>0.1934355965278536</v>
       </c>
       <c r="C70">
-        <v>-161.9444653755264</v>
+        <v>-165.8356068947241</v>
       </c>
       <c r="D70">
-        <v>51.13953462447363</v>
+        <v>50.48139310527591</v>
       </c>
       <c r="E70">
-        <v>73.84400000000002</v>
+        <v>77.07700000000003</v>
       </c>
       <c r="F70">
-        <v>219.844</v>
+        <v>223.077</v>
       </c>
       <c r="G70">
         <v>6.76</v>
@@ -7021,37 +7021,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M70">
-        <v>51.83921520000001</v>
+        <v>52.60155660000001</v>
       </c>
       <c r="N70">
-        <v>-37.87254853333334</v>
+        <v>-38.63488993333335</v>
       </c>
       <c r="O70">
-        <v>-9.089411648000002</v>
+        <v>-9.272373584000004</v>
       </c>
       <c r="P70">
-        <v>-28.78313688533334</v>
+        <v>-29.36251634933334</v>
       </c>
       <c r="Q70">
-        <v>7.916863114666661</v>
+        <v>7.337483650666659</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.129873986597733</v>
+        <v>0.1325860506815308</v>
       </c>
       <c r="T70">
-        <v>1.728649653853501</v>
+        <v>1.784412545913292</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06466147273001151</v>
+        <v>0.06372434993682294</v>
       </c>
       <c r="W70">
-        <v>0.2205528247302633</v>
+        <v>0.2207737982848972</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2694228030417146</v>
+        <v>0.2655181247367623</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1934355965278536</v>
+        <v>0.1953355965278536</v>
       </c>
       <c r="C71">
-        <v>-165.8356068947241</v>
+        <v>-169.7100237153817</v>
       </c>
       <c r="D71">
-        <v>50.48139310527591</v>
+        <v>49.83997628461835</v>
       </c>
       <c r="E71">
-        <v>77.07700000000003</v>
+        <v>80.31000000000003</v>
       </c>
       <c r="F71">
-        <v>223.077</v>
+        <v>226.31</v>
       </c>
       <c r="G71">
         <v>6.76</v>
@@ -7103,37 +7103,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M71">
-        <v>52.60155660000001</v>
+        <v>53.36389800000001</v>
       </c>
       <c r="N71">
-        <v>-38.63488993333335</v>
+        <v>-39.39723133333334</v>
       </c>
       <c r="O71">
-        <v>-9.272373584000004</v>
+        <v>-9.455335520000002</v>
       </c>
       <c r="P71">
-        <v>-29.36251634933334</v>
+        <v>-29.94189581333334</v>
       </c>
       <c r="Q71">
-        <v>7.337483650666659</v>
+        <v>6.75810418666666</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1325860506815308</v>
+        <v>0.1354789190375818</v>
       </c>
       <c r="T71">
-        <v>1.784412545913292</v>
+        <v>1.843892964110401</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06372434993682294</v>
+        <v>0.0628140020805826</v>
       </c>
       <c r="W71">
-        <v>0.2207737982848972</v>
+        <v>0.2209884583093986</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2655181247367623</v>
+        <v>0.2617250086690942</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1953355965278536</v>
+        <v>0.1972355965278536</v>
       </c>
       <c r="C72">
-        <v>-169.7100237153817</v>
+        <v>-173.5683453511924</v>
       </c>
       <c r="D72">
-        <v>49.83997628461835</v>
+        <v>49.21465464880765</v>
       </c>
       <c r="E72">
-        <v>80.31000000000003</v>
+        <v>83.54300000000003</v>
       </c>
       <c r="F72">
-        <v>226.31</v>
+        <v>229.543</v>
       </c>
       <c r="G72">
         <v>6.76</v>
@@ -7185,37 +7185,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M72">
-        <v>53.36389800000001</v>
+        <v>54.12623940000001</v>
       </c>
       <c r="N72">
-        <v>-39.39723133333334</v>
+        <v>-40.15957273333335</v>
       </c>
       <c r="O72">
-        <v>-9.455335520000002</v>
+        <v>-9.638297456000004</v>
       </c>
       <c r="P72">
-        <v>-29.94189581333334</v>
+        <v>-30.52127527733334</v>
       </c>
       <c r="Q72">
-        <v>6.75810418666666</v>
+        <v>6.178724722666658</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1354789190375818</v>
+        <v>0.1385712955561192</v>
       </c>
       <c r="T72">
-        <v>1.843892964110401</v>
+        <v>1.907475480114208</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0628140020805826</v>
+        <v>0.06192929782592652</v>
       </c>
       <c r="W72">
-        <v>0.2209884583093986</v>
+        <v>0.2211970715726465</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2617250086690942</v>
+        <v>0.2580387409413605</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1972355965278536</v>
+        <v>0.1991355965278536</v>
       </c>
       <c r="C73">
-        <v>-173.5683453511924</v>
+        <v>-177.4111701143272</v>
       </c>
       <c r="D73">
-        <v>49.21465464880765</v>
+        <v>48.60482988567278</v>
       </c>
       <c r="E73">
-        <v>83.54300000000001</v>
+        <v>86.77600000000001</v>
       </c>
       <c r="F73">
-        <v>229.543</v>
+        <v>232.776</v>
       </c>
       <c r="G73">
         <v>6.76</v>
@@ -7267,37 +7267,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M73">
-        <v>54.1262394</v>
+        <v>54.88858080000001</v>
       </c>
       <c r="N73">
-        <v>-40.15957273333334</v>
+        <v>-40.92191413333335</v>
       </c>
       <c r="O73">
-        <v>-9.638297456000002</v>
+        <v>-9.821259392000002</v>
       </c>
       <c r="P73">
-        <v>-30.52127527733334</v>
+        <v>-31.10065474133334</v>
       </c>
       <c r="Q73">
-        <v>6.178724722666665</v>
+        <v>5.599345258666659</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1385712955561191</v>
+        <v>0.1418845561116948</v>
       </c>
       <c r="T73">
-        <v>1.907475480114208</v>
+        <v>1.975599604404001</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06192929782592652</v>
+        <v>0.06106916868945532</v>
       </c>
       <c r="W73">
-        <v>0.2211970715726465</v>
+        <v>0.2213998900230264</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2580387409413605</v>
+        <v>0.2544548695393971</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1991355965278536</v>
+        <v>0.2010355965278536</v>
       </c>
       <c r="C74">
-        <v>-177.4111701143272</v>
+        <v>-181.2390670248835</v>
       </c>
       <c r="D74">
-        <v>48.60482988567278</v>
+        <v>48.00993297511656</v>
       </c>
       <c r="E74">
-        <v>86.77600000000001</v>
+        <v>90.00900000000001</v>
       </c>
       <c r="F74">
-        <v>232.776</v>
+        <v>236.009</v>
       </c>
       <c r="G74">
         <v>6.76</v>
@@ -7349,37 +7349,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M74">
-        <v>54.88858080000001</v>
+        <v>55.6509222</v>
       </c>
       <c r="N74">
-        <v>-40.92191413333335</v>
+        <v>-41.68425553333334</v>
       </c>
       <c r="O74">
-        <v>-9.821259392000002</v>
+        <v>-10.004221328</v>
       </c>
       <c r="P74">
-        <v>-31.10065474133334</v>
+        <v>-31.68003420533334</v>
       </c>
       <c r="Q74">
-        <v>5.599345258666659</v>
+        <v>5.01996579466666</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1418845561116948</v>
+        <v>0.1454432433750909</v>
       </c>
       <c r="T74">
-        <v>1.975599604404001</v>
+        <v>2.048769960122667</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06106916868945532</v>
+        <v>0.06023260473480525</v>
       </c>
       <c r="W74">
-        <v>0.2213998900230264</v>
+        <v>0.2215971518035329</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2544548695393971</v>
+        <v>0.2509691863950219</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2010355965278536</v>
+        <v>0.2029355965278536</v>
       </c>
       <c r="C75">
-        <v>-181.2390670248835</v>
+        <v>-185.0525775818059</v>
       </c>
       <c r="D75">
-        <v>48.00993297511656</v>
+        <v>47.42942241819415</v>
       </c>
       <c r="E75">
-        <v>90.00900000000001</v>
+        <v>93.24200000000002</v>
       </c>
       <c r="F75">
-        <v>236.009</v>
+        <v>239.242</v>
       </c>
       <c r="G75">
         <v>6.76</v>
@@ -7431,37 +7431,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M75">
-        <v>55.6509222</v>
+        <v>56.41326360000001</v>
       </c>
       <c r="N75">
-        <v>-41.68425553333334</v>
+        <v>-42.44659693333335</v>
       </c>
       <c r="O75">
-        <v>-10.004221328</v>
+        <v>-10.187183264</v>
       </c>
       <c r="P75">
-        <v>-31.68003420533334</v>
+        <v>-32.25941366933334</v>
       </c>
       <c r="Q75">
-        <v>5.01996579466666</v>
+        <v>4.440586330666662</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1454432433750909</v>
+        <v>0.1492756758125944</v>
       </c>
       <c r="T75">
-        <v>2.048769960122667</v>
+        <v>2.12756880474277</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06023260473480525</v>
+        <v>0.05941865061676734</v>
       </c>
       <c r="W75">
-        <v>0.2215971518035329</v>
+        <v>0.2217890821845663</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2509691863950219</v>
+        <v>0.2475777109031972</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2029355965278536</v>
+        <v>0.2048355965278536</v>
       </c>
       <c r="C76">
-        <v>-185.0525775818059</v>
+        <v>-188.8522174068641</v>
       </c>
       <c r="D76">
-        <v>47.42942241819415</v>
+        <v>46.8627825931359</v>
       </c>
       <c r="E76">
-        <v>93.24200000000002</v>
+        <v>96.47500000000002</v>
       </c>
       <c r="F76">
-        <v>239.242</v>
+        <v>242.475</v>
       </c>
       <c r="G76">
         <v>6.76</v>
@@ -7513,37 +7513,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M76">
-        <v>56.41326360000001</v>
+        <v>57.175605</v>
       </c>
       <c r="N76">
-        <v>-42.44659693333335</v>
+        <v>-43.20893833333334</v>
       </c>
       <c r="O76">
-        <v>-10.187183264</v>
+        <v>-10.3701452</v>
       </c>
       <c r="P76">
-        <v>-32.25941366933334</v>
+        <v>-32.83879313333334</v>
       </c>
       <c r="Q76">
-        <v>4.440586330666662</v>
+        <v>3.861206866666663</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1492756758125944</v>
+        <v>0.1534147028450982</v>
       </c>
       <c r="T76">
-        <v>2.12756880474277</v>
+        <v>2.212671556932481</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05941865061676734</v>
+        <v>0.05862640194187711</v>
       </c>
       <c r="W76">
-        <v>0.2217890821845663</v>
+        <v>0.2219758944221054</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2475777109031972</v>
+        <v>0.2442766747578213</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2048355965278536</v>
+        <v>0.2067355965278536</v>
       </c>
       <c r="C77">
-        <v>-188.8522174068641</v>
+        <v>-192.6384777721777</v>
       </c>
       <c r="D77">
-        <v>46.8627825931359</v>
+        <v>46.30952222782231</v>
       </c>
       <c r="E77">
-        <v>96.47500000000002</v>
+        <v>99.708</v>
       </c>
       <c r="F77">
-        <v>242.475</v>
+        <v>245.708</v>
       </c>
       <c r="G77">
         <v>6.76</v>
@@ -7595,37 +7595,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M77">
-        <v>57.175605</v>
+        <v>57.9379464</v>
       </c>
       <c r="N77">
-        <v>-43.20893833333334</v>
+        <v>-43.97127973333334</v>
       </c>
       <c r="O77">
-        <v>-10.3701452</v>
+        <v>-10.553107136</v>
       </c>
       <c r="P77">
-        <v>-32.83879313333334</v>
+        <v>-33.41817259733334</v>
       </c>
       <c r="Q77">
-        <v>3.861206866666663</v>
+        <v>3.281827402666664</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1534147028450982</v>
+        <v>0.1578986487969773</v>
       </c>
       <c r="T77">
-        <v>2.212671556932481</v>
+        <v>2.304866205138001</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05862640194187711</v>
+        <v>0.05785500191632609</v>
       </c>
       <c r="W77">
-        <v>0.2219758944221054</v>
+        <v>0.2221577905481303</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2442766747578213</v>
+        <v>0.2410625079846921</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2067355965278536</v>
+        <v>0.2086355965278536</v>
       </c>
       <c r="C78">
-        <v>-192.6384777721777</v>
+        <v>-196.4118270208004</v>
       </c>
       <c r="D78">
-        <v>46.30952222782231</v>
+        <v>45.76917297919958</v>
       </c>
       <c r="E78">
-        <v>99.708</v>
+        <v>102.941</v>
       </c>
       <c r="F78">
-        <v>245.708</v>
+        <v>248.941</v>
       </c>
       <c r="G78">
         <v>6.76</v>
@@ -7677,37 +7677,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M78">
-        <v>57.9379464</v>
+        <v>58.70028780000001</v>
       </c>
       <c r="N78">
-        <v>-43.97127973333334</v>
+        <v>-44.73362113333334</v>
       </c>
       <c r="O78">
-        <v>-10.553107136</v>
+        <v>-10.736069072</v>
       </c>
       <c r="P78">
-        <v>-33.41817259733334</v>
+        <v>-33.99755206133334</v>
       </c>
       <c r="Q78">
-        <v>3.281827402666664</v>
+        <v>2.702447938666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1578986487969773</v>
+        <v>0.162772503092498</v>
       </c>
       <c r="T78">
-        <v>2.304866205138001</v>
+        <v>2.405077779274436</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05785500191632609</v>
+        <v>0.05710363825507511</v>
       </c>
       <c r="W78">
-        <v>0.2221577905481303</v>
+        <v>0.2223349620994533</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2410625079846921</v>
+        <v>0.2379318260628129</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2086355965278536</v>
+        <v>0.2105355965278536</v>
       </c>
       <c r="C79">
-        <v>-196.4118270208004</v>
+        <v>-200.1727118889975</v>
       </c>
       <c r="D79">
-        <v>45.76917297919958</v>
+        <v>45.24128811100251</v>
       </c>
       <c r="E79">
-        <v>102.941</v>
+        <v>106.174</v>
       </c>
       <c r="F79">
-        <v>248.941</v>
+        <v>252.174</v>
       </c>
       <c r="G79">
         <v>6.76</v>
@@ -7759,37 +7759,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M79">
-        <v>58.70028780000001</v>
+        <v>59.4626292</v>
       </c>
       <c r="N79">
-        <v>-44.73362113333334</v>
+        <v>-45.49596253333334</v>
       </c>
       <c r="O79">
-        <v>-10.736069072</v>
+        <v>-10.919031008</v>
       </c>
       <c r="P79">
-        <v>-33.99755206133334</v>
+        <v>-34.57693152533334</v>
       </c>
       <c r="Q79">
-        <v>2.702447938666666</v>
+        <v>2.123068474666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.162772503092498</v>
+        <v>0.168089435051248</v>
       </c>
       <c r="T79">
-        <v>2.405077779274436</v>
+        <v>2.514399496514183</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05710363825507511</v>
+        <v>0.05637154032872799</v>
       </c>
       <c r="W79">
-        <v>0.2223349620994533</v>
+        <v>0.2225075907904859</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2379318260628129</v>
+        <v>0.2348814180363666</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2105355965278536</v>
+        <v>0.2124355965278536</v>
       </c>
       <c r="C80">
-        <v>-200.1727118889975</v>
+        <v>-203.9215587380621</v>
       </c>
       <c r="D80">
-        <v>45.24128811100251</v>
+        <v>44.72544126193786</v>
       </c>
       <c r="E80">
-        <v>106.174</v>
+        <v>109.407</v>
       </c>
       <c r="F80">
-        <v>252.174</v>
+        <v>255.407</v>
       </c>
       <c r="G80">
         <v>6.76</v>
@@ -7841,37 +7841,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M80">
-        <v>59.4626292</v>
+        <v>60.22497060000001</v>
       </c>
       <c r="N80">
-        <v>-45.49596253333334</v>
+        <v>-46.25830393333334</v>
       </c>
       <c r="O80">
-        <v>-10.919031008</v>
+        <v>-11.101992944</v>
       </c>
       <c r="P80">
-        <v>-34.57693152533334</v>
+        <v>-35.15631098933334</v>
       </c>
       <c r="Q80">
-        <v>2.123068474666667</v>
+        <v>1.543689010666661</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.168089435051248</v>
+        <v>0.1739127414822598</v>
       </c>
       <c r="T80">
-        <v>2.514399496514183</v>
+        <v>2.634132805872002</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05637154032872799</v>
+        <v>0.05565797652709852</v>
       </c>
       <c r="W80">
-        <v>0.2225075907904859</v>
+        <v>0.2226758491349102</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2348814180363666</v>
+        <v>0.2319082355295772</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2124355965278536</v>
+        <v>0.2143355965278536</v>
       </c>
       <c r="C81">
-        <v>-203.9215587380621</v>
+        <v>-207.6587747028103</v>
       </c>
       <c r="D81">
-        <v>44.72544126193786</v>
+        <v>44.22122529718977</v>
       </c>
       <c r="E81">
-        <v>109.407</v>
+        <v>112.64</v>
       </c>
       <c r="F81">
-        <v>255.407</v>
+        <v>258.64</v>
       </c>
       <c r="G81">
         <v>6.76</v>
@@ -7923,37 +7923,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M81">
-        <v>60.22497060000001</v>
+        <v>60.98731200000001</v>
       </c>
       <c r="N81">
-        <v>-46.25830393333334</v>
+        <v>-47.02064533333335</v>
       </c>
       <c r="O81">
-        <v>-11.101992944</v>
+        <v>-11.28495488</v>
       </c>
       <c r="P81">
-        <v>-35.15631098933334</v>
+        <v>-35.73569045333335</v>
       </c>
       <c r="Q81">
-        <v>1.543689010666661</v>
+        <v>0.9643095466666551</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1739127414822598</v>
+        <v>0.1803183785563728</v>
       </c>
       <c r="T81">
-        <v>2.634132805872002</v>
+        <v>2.765839446165602</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05565797652709852</v>
+        <v>0.05496225182050978</v>
       </c>
       <c r="W81">
-        <v>0.2226758491349102</v>
+        <v>0.2228399010207238</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2319082355295772</v>
+        <v>0.2290093825854574</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2143355965278536</v>
+        <v>0.2162355965278536</v>
       </c>
       <c r="C82">
-        <v>-207.6587747028103</v>
+        <v>-211.384748763255</v>
       </c>
       <c r="D82">
-        <v>44.22122529718977</v>
+        <v>43.72825123674503</v>
       </c>
       <c r="E82">
-        <v>112.64</v>
+        <v>115.873</v>
       </c>
       <c r="F82">
-        <v>258.64</v>
+        <v>261.873</v>
       </c>
       <c r="G82">
         <v>6.76</v>
@@ -8005,37 +8005,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M82">
-        <v>60.98731200000001</v>
+        <v>61.74965340000001</v>
       </c>
       <c r="N82">
-        <v>-47.02064533333335</v>
+        <v>-47.78298673333335</v>
       </c>
       <c r="O82">
-        <v>-11.28495488</v>
+        <v>-11.467916816</v>
       </c>
       <c r="P82">
-        <v>-35.73569045333335</v>
+        <v>-36.31506991733335</v>
       </c>
       <c r="Q82">
-        <v>0.9643095466666551</v>
+        <v>0.3849300826666564</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1803183785563728</v>
+        <v>0.1873982932172345</v>
       </c>
       <c r="T82">
-        <v>2.765839446165602</v>
+        <v>2.911409943332213</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05496225182050978</v>
+        <v>0.05428370550173805</v>
       </c>
       <c r="W82">
-        <v>0.2228399010207238</v>
+        <v>0.2229999022426902</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2290093825854574</v>
+        <v>0.2261821062572419</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2162355965278536</v>
+        <v>0.2181355965278536</v>
       </c>
       <c r="C83">
-        <v>-211.384748763255</v>
+        <v>-215.0998527453908</v>
       </c>
       <c r="D83">
-        <v>43.72825123674503</v>
+        <v>43.24614725460928</v>
       </c>
       <c r="E83">
-        <v>115.873</v>
+        <v>119.1060000000001</v>
       </c>
       <c r="F83">
-        <v>261.873</v>
+        <v>265.1060000000001</v>
       </c>
       <c r="G83">
         <v>6.76</v>
@@ -8087,37 +8087,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M83">
-        <v>61.74965340000001</v>
+        <v>62.51199480000002</v>
       </c>
       <c r="N83">
-        <v>-47.78298673333335</v>
+        <v>-48.54532813333336</v>
       </c>
       <c r="O83">
-        <v>-11.467916816</v>
+        <v>-11.65087875200001</v>
       </c>
       <c r="P83">
-        <v>-36.31506991733335</v>
+        <v>-36.89444938133335</v>
       </c>
       <c r="Q83">
-        <v>0.3849300826666564</v>
+        <v>-0.1944493813333494</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1873982932172345</v>
+        <v>0.1952648650626364</v>
       </c>
       <c r="T83">
-        <v>2.911409943332213</v>
+        <v>3.073154940184002</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05428370550173805</v>
+        <v>0.05362170909318027</v>
       </c>
       <c r="W83">
-        <v>0.2229999022426902</v>
+        <v>0.2231560009958281</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2261821062572419</v>
+        <v>0.2234237878882511</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2181355965278536</v>
+        <v>0.2200355965278536</v>
       </c>
       <c r="C84">
-        <v>-215.0998527453908</v>
+        <v>-218.8044422564963</v>
       </c>
       <c r="D84">
-        <v>43.24614725460928</v>
+        <v>42.77455774350373</v>
       </c>
       <c r="E84">
-        <v>119.1060000000001</v>
+        <v>122.3390000000001</v>
       </c>
       <c r="F84">
-        <v>265.1060000000001</v>
+        <v>268.3390000000001</v>
       </c>
       <c r="G84">
         <v>6.76</v>
@@ -8169,37 +8169,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M84">
-        <v>62.51199480000002</v>
+        <v>63.27433620000001</v>
       </c>
       <c r="N84">
-        <v>-48.54532813333336</v>
+        <v>-49.30766953333335</v>
       </c>
       <c r="O84">
-        <v>-11.65087875200001</v>
+        <v>-11.833840688</v>
       </c>
       <c r="P84">
-        <v>-36.89444938133335</v>
+        <v>-37.47382884533335</v>
       </c>
       <c r="Q84">
-        <v>-0.1944493813333494</v>
+        <v>-0.7738288453333482</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1952648650626364</v>
+        <v>0.2040569159486739</v>
       </c>
       <c r="T84">
-        <v>3.073154940184002</v>
+        <v>3.253928760194826</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05362170909318027</v>
+        <v>0.05297566440531063</v>
       </c>
       <c r="W84">
-        <v>0.2231560009958281</v>
+        <v>0.2233083383332277</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2234237878882511</v>
+        <v>0.2207319350221276</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2200355965278536</v>
+        <v>0.2219355965278536</v>
       </c>
       <c r="C85">
-        <v>-218.8044422564963</v>
+        <v>-222.4988575599033</v>
       </c>
       <c r="D85">
-        <v>42.77455774350373</v>
+        <v>42.3131424400968</v>
       </c>
       <c r="E85">
-        <v>122.3390000000001</v>
+        <v>125.5720000000001</v>
       </c>
       <c r="F85">
-        <v>268.3390000000001</v>
+        <v>271.5720000000001</v>
       </c>
       <c r="G85">
         <v>6.76</v>
@@ -8251,37 +8251,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M85">
-        <v>63.27433620000001</v>
+        <v>64.03667760000002</v>
       </c>
       <c r="N85">
-        <v>-49.30766953333335</v>
+        <v>-50.07001093333336</v>
       </c>
       <c r="O85">
-        <v>-11.833840688</v>
+        <v>-12.01680262400001</v>
       </c>
       <c r="P85">
-        <v>-37.47382884533335</v>
+        <v>-38.05320830933335</v>
       </c>
       <c r="Q85">
-        <v>-0.7738288453333482</v>
+        <v>-1.353208309333347</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2040569159486739</v>
+        <v>0.213947973195466</v>
       </c>
       <c r="T85">
-        <v>3.253928760194826</v>
+        <v>3.457299307707004</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05297566440531063</v>
+        <v>0.05234500173381883</v>
       </c>
       <c r="W85">
-        <v>0.2233083383332277</v>
+        <v>0.2234570485911655</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2207319350221276</v>
+        <v>0.2181041738909119</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2219355965278536</v>
+        <v>0.2238355965278536</v>
       </c>
       <c r="C86">
-        <v>-222.4988575599032</v>
+        <v>-226.1834243937504</v>
       </c>
       <c r="D86">
-        <v>42.31314244009676</v>
+        <v>41.86157560624959</v>
       </c>
       <c r="E86">
-        <v>125.572</v>
+        <v>128.805</v>
       </c>
       <c r="F86">
-        <v>271.572</v>
+        <v>274.805</v>
       </c>
       <c r="G86">
         <v>6.76</v>
@@ -8333,37 +8333,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M86">
-        <v>64.0366776</v>
+        <v>64.799019</v>
       </c>
       <c r="N86">
-        <v>-50.07001093333334</v>
+        <v>-50.83235233333334</v>
       </c>
       <c r="O86">
-        <v>-12.016802624</v>
+        <v>-12.19976456</v>
       </c>
       <c r="P86">
-        <v>-38.05320830933334</v>
+        <v>-38.63258777333334</v>
       </c>
       <c r="Q86">
-        <v>-1.35320830933334</v>
+        <v>-1.932587773333339</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2139479731954659</v>
+        <v>0.2251578380751637</v>
       </c>
       <c r="T86">
-        <v>3.457299307707001</v>
+        <v>3.687785928220801</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05234500173381884</v>
+        <v>0.05172917818400922</v>
       </c>
       <c r="W86">
-        <v>0.2234570485911655</v>
+        <v>0.2236022597842106</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2181041738909119</v>
+        <v>0.2155382424333717</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2238355965278536</v>
+        <v>0.2257355965278536</v>
       </c>
       <c r="C87">
-        <v>-226.1834243937504</v>
+        <v>-229.8584547378661</v>
       </c>
       <c r="D87">
-        <v>41.86157560624959</v>
+        <v>41.41954526213387</v>
       </c>
       <c r="E87">
-        <v>128.805</v>
+        <v>132.038</v>
       </c>
       <c r="F87">
-        <v>274.805</v>
+        <v>278.038</v>
       </c>
       <c r="G87">
         <v>6.76</v>
@@ -8415,37 +8415,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M87">
-        <v>64.799019</v>
+        <v>65.56136040000001</v>
       </c>
       <c r="N87">
-        <v>-50.83235233333334</v>
+        <v>-51.59469373333335</v>
       </c>
       <c r="O87">
-        <v>-12.19976456</v>
+        <v>-12.382726496</v>
       </c>
       <c r="P87">
-        <v>-38.63258777333334</v>
+        <v>-39.21196723733335</v>
       </c>
       <c r="Q87">
-        <v>-1.932587773333339</v>
+        <v>-2.511967237333344</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2251578380751637</v>
+        <v>0.2379691122233896</v>
       </c>
       <c r="T87">
-        <v>3.687785928220801</v>
+        <v>3.951199208808001</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05172917818400922</v>
+        <v>0.05112767611210212</v>
       </c>
       <c r="W87">
-        <v>0.2236022597842106</v>
+        <v>0.2237440939727663</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2155382424333717</v>
+        <v>0.2130319838004255</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2257355965278536</v>
+        <v>0.2276355965278536</v>
       </c>
       <c r="C88">
-        <v>-229.8584547378661</v>
+        <v>-233.5242475325707</v>
       </c>
       <c r="D88">
-        <v>41.41954526213387</v>
+        <v>40.98675246742933</v>
       </c>
       <c r="E88">
-        <v>132.038</v>
+        <v>135.271</v>
       </c>
       <c r="F88">
-        <v>278.038</v>
+        <v>281.271</v>
       </c>
       <c r="G88">
         <v>6.76</v>
@@ -8497,37 +8497,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M88">
-        <v>65.56136040000001</v>
+        <v>66.32370180000001</v>
       </c>
       <c r="N88">
-        <v>-51.59469373333335</v>
+        <v>-52.35703513333335</v>
       </c>
       <c r="O88">
-        <v>-12.382726496</v>
+        <v>-12.565688432</v>
       </c>
       <c r="P88">
-        <v>-39.21196723733335</v>
+        <v>-39.79134670133335</v>
       </c>
       <c r="Q88">
-        <v>-2.511967237333344</v>
+        <v>-3.091346701333343</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2379691122233896</v>
+        <v>0.2527513516251888</v>
       </c>
       <c r="T88">
-        <v>3.951199208808001</v>
+        <v>4.25513760948554</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05112767611210212</v>
+        <v>0.05054000167403198</v>
       </c>
       <c r="W88">
-        <v>0.2237440939727663</v>
+        <v>0.2238826676052633</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2130319838004255</v>
+        <v>0.2105833403084666</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2276355965278536</v>
+        <v>0.2295355965278536</v>
       </c>
       <c r="C89">
-        <v>-233.5242475325707</v>
+        <v>-237.1810893528808</v>
       </c>
       <c r="D89">
-        <v>40.98675246742933</v>
+        <v>40.56291064711925</v>
       </c>
       <c r="E89">
-        <v>135.271</v>
+        <v>138.504</v>
       </c>
       <c r="F89">
-        <v>281.271</v>
+        <v>284.504</v>
       </c>
       <c r="G89">
         <v>6.76</v>
@@ -8579,37 +8579,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M89">
-        <v>66.32370180000001</v>
+        <v>67.08604320000001</v>
       </c>
       <c r="N89">
-        <v>-52.35703513333335</v>
+        <v>-53.11937653333334</v>
       </c>
       <c r="O89">
-        <v>-12.565688432</v>
+        <v>-12.748650368</v>
       </c>
       <c r="P89">
-        <v>-39.79134670133335</v>
+        <v>-40.37072616533334</v>
       </c>
       <c r="Q89">
-        <v>-3.091346701333343</v>
+        <v>-3.670726165333342</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2527513516251888</v>
+        <v>0.2699972975939546</v>
       </c>
       <c r="T89">
-        <v>4.25513760948554</v>
+        <v>4.609732410276002</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05054000167403198</v>
+        <v>0.04996568347319071</v>
       </c>
       <c r="W89">
-        <v>0.2238826676052633</v>
+        <v>0.2240180918370216</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2105833403084666</v>
+        <v>0.2081903478049614</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2295355965278536</v>
+        <v>0.2314355965278536</v>
       </c>
       <c r="C90">
-        <v>-237.1810893528808</v>
+        <v>-240.8292550413103</v>
       </c>
       <c r="D90">
-        <v>40.56291064711925</v>
+        <v>40.14774495868969</v>
       </c>
       <c r="E90">
-        <v>138.504</v>
+        <v>141.737</v>
       </c>
       <c r="F90">
-        <v>284.504</v>
+        <v>287.737</v>
       </c>
       <c r="G90">
         <v>6.76</v>
@@ -8661,37 +8661,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M90">
-        <v>67.08604320000001</v>
+        <v>67.8483846</v>
       </c>
       <c r="N90">
-        <v>-53.11937653333334</v>
+        <v>-53.88171793333334</v>
       </c>
       <c r="O90">
-        <v>-12.748650368</v>
+        <v>-12.931612304</v>
       </c>
       <c r="P90">
-        <v>-40.37072616533334</v>
+        <v>-40.95010562933334</v>
       </c>
       <c r="Q90">
-        <v>-3.670726165333342</v>
+        <v>-4.250105629333333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2699972975939546</v>
+        <v>0.2903788701024959</v>
       </c>
       <c r="T90">
-        <v>4.609732410276002</v>
+        <v>5.028798993028366</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04996568347319071</v>
+        <v>0.04940427129933465</v>
       </c>
       <c r="W90">
-        <v>0.2240180918370216</v>
+        <v>0.2241504728276169</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2081903478049614</v>
+        <v>0.2058511304138944</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2314355965278536</v>
+        <v>0.2333355965278536</v>
       </c>
       <c r="C91">
-        <v>-240.8292550413103</v>
+        <v>-244.4690083022049</v>
       </c>
       <c r="D91">
-        <v>40.14774495868969</v>
+        <v>39.74099169779509</v>
       </c>
       <c r="E91">
-        <v>141.737</v>
+        <v>144.97</v>
       </c>
       <c r="F91">
-        <v>287.737</v>
+        <v>290.97</v>
       </c>
       <c r="G91">
         <v>6.76</v>
@@ -8743,37 +8743,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M91">
-        <v>67.8483846</v>
+        <v>68.61072600000001</v>
       </c>
       <c r="N91">
-        <v>-53.88171793333334</v>
+        <v>-54.64405933333335</v>
       </c>
       <c r="O91">
-        <v>-12.931612304</v>
+        <v>-13.11457424</v>
       </c>
       <c r="P91">
-        <v>-40.95010562933334</v>
+        <v>-41.52948509333335</v>
       </c>
       <c r="Q91">
-        <v>-4.250105629333333</v>
+        <v>-4.829485093333346</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2903788701024959</v>
+        <v>0.3148367571127456</v>
       </c>
       <c r="T91">
-        <v>5.028798993028366</v>
+        <v>5.531678892331204</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04940427129933465</v>
+        <v>0.04885533495156425</v>
       </c>
       <c r="W91">
-        <v>0.2241504728276169</v>
+        <v>0.2242799120184212</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2058511304138944</v>
+        <v>0.2035638956315177</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2333355965278536</v>
+        <v>0.2352355965278536</v>
       </c>
       <c r="C92">
-        <v>-244.4690083022049</v>
+        <v>-248.1006022603088</v>
       </c>
       <c r="D92">
-        <v>39.74099169779509</v>
+        <v>39.34239773969123</v>
       </c>
       <c r="E92">
-        <v>144.97</v>
+        <v>148.203</v>
       </c>
       <c r="F92">
-        <v>290.97</v>
+        <v>294.203</v>
       </c>
       <c r="G92">
         <v>6.76</v>
@@ -8825,37 +8825,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M92">
-        <v>68.61072600000001</v>
+        <v>69.37306740000001</v>
       </c>
       <c r="N92">
-        <v>-54.64405933333335</v>
+        <v>-55.40640073333335</v>
       </c>
       <c r="O92">
-        <v>-13.11457424</v>
+        <v>-13.297536176</v>
       </c>
       <c r="P92">
-        <v>-41.52948509333335</v>
+        <v>-42.10886455733335</v>
       </c>
       <c r="Q92">
-        <v>-4.829485093333346</v>
+        <v>-5.408864557333345</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3148367571127456</v>
+        <v>0.3447297301252729</v>
       </c>
       <c r="T92">
-        <v>5.531678892331204</v>
+        <v>6.146309880368005</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04885533495156425</v>
+        <v>0.0483184631389097</v>
       </c>
       <c r="W92">
-        <v>0.2242799120184212</v>
+        <v>0.2244065063918451</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2035638956315177</v>
+        <v>0.2013269297454571</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2352355965278536</v>
+        <v>0.2371355965278536</v>
       </c>
       <c r="C93">
-        <v>-248.1006022603088</v>
+        <v>-251.7242799860531</v>
       </c>
       <c r="D93">
-        <v>39.34239773969123</v>
+        <v>38.95172001394696</v>
       </c>
       <c r="E93">
-        <v>148.203</v>
+        <v>151.436</v>
       </c>
       <c r="F93">
-        <v>294.203</v>
+        <v>297.436</v>
       </c>
       <c r="G93">
         <v>6.76</v>
@@ -8907,37 +8907,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M93">
-        <v>69.37306740000001</v>
+        <v>70.13540880000001</v>
       </c>
       <c r="N93">
-        <v>-55.40640073333335</v>
+        <v>-56.16874213333335</v>
       </c>
       <c r="O93">
-        <v>-13.297536176</v>
+        <v>-13.480498112</v>
       </c>
       <c r="P93">
-        <v>-42.10886455733335</v>
+        <v>-42.68824402133335</v>
       </c>
       <c r="Q93">
-        <v>-5.408864557333345</v>
+        <v>-5.988244021333344</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3447297301252729</v>
+        <v>0.3820959463909321</v>
       </c>
       <c r="T93">
-        <v>6.146309880368005</v>
+        <v>6.914598615414008</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0483184631389097</v>
+        <v>0.0477932624526172</v>
       </c>
       <c r="W93">
-        <v>0.2244065063918451</v>
+        <v>0.2245303487136729</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2013269297454571</v>
+        <v>0.1991385935525717</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2371355965278536</v>
+        <v>0.2390355965278536</v>
       </c>
       <c r="C94">
-        <v>-251.7242799860531</v>
+        <v>-255.3402749898531</v>
       </c>
       <c r="D94">
-        <v>38.95172001394696</v>
+        <v>38.5687250101469</v>
       </c>
       <c r="E94">
-        <v>151.436</v>
+        <v>154.669</v>
       </c>
       <c r="F94">
-        <v>297.436</v>
+        <v>300.669</v>
       </c>
       <c r="G94">
         <v>6.76</v>
@@ -8989,37 +8989,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M94">
-        <v>70.13540880000001</v>
+        <v>70.89775020000002</v>
       </c>
       <c r="N94">
-        <v>-56.16874213333335</v>
+        <v>-56.93108353333336</v>
       </c>
       <c r="O94">
-        <v>-13.480498112</v>
+        <v>-13.663460048</v>
       </c>
       <c r="P94">
-        <v>-42.68824402133335</v>
+        <v>-43.26762348533335</v>
       </c>
       <c r="Q94">
-        <v>-5.988244021333344</v>
+        <v>-6.56762348533335</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3820959463909321</v>
+        <v>0.4301382244467796</v>
       </c>
       <c r="T94">
-        <v>6.914598615414008</v>
+        <v>7.902398417616009</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0477932624526172</v>
+        <v>0.0472793564047396</v>
       </c>
       <c r="W94">
-        <v>0.2245303487136729</v>
+        <v>0.2246515277597624</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1991385935525717</v>
+        <v>0.1969973183530817</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2390355965278536</v>
+        <v>0.2409355965278536</v>
       </c>
       <c r="C95">
-        <v>-255.3402749898531</v>
+        <v>-258.9488116875301</v>
       </c>
       <c r="D95">
-        <v>38.5687250101469</v>
+        <v>38.19318831247001</v>
       </c>
       <c r="E95">
-        <v>154.669</v>
+        <v>157.902</v>
       </c>
       <c r="F95">
-        <v>300.669</v>
+        <v>303.902</v>
       </c>
       <c r="G95">
         <v>6.76</v>
@@ -9071,37 +9071,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M95">
-        <v>70.89775020000002</v>
+        <v>71.66009160000002</v>
       </c>
       <c r="N95">
-        <v>-56.93108353333336</v>
+        <v>-57.69342493333335</v>
       </c>
       <c r="O95">
-        <v>-13.663460048</v>
+        <v>-13.846421984</v>
       </c>
       <c r="P95">
-        <v>-43.26762348533335</v>
+        <v>-43.84700294933335</v>
       </c>
       <c r="Q95">
-        <v>-6.56762348533335</v>
+        <v>-7.147002949333348</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4301382244467796</v>
+        <v>0.4941945951879096</v>
       </c>
       <c r="T95">
-        <v>7.902398417616009</v>
+        <v>9.219464820552012</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0472793564047396</v>
+        <v>0.04677638452809343</v>
       </c>
       <c r="W95">
-        <v>0.2246515277597624</v>
+        <v>0.2247701285282756</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1969973183530817</v>
+        <v>0.1949016022003893</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2409355965278536</v>
+        <v>0.2428355965278536</v>
       </c>
       <c r="C96">
-        <v>-258.9488116875301</v>
+        <v>-262.5501058388026</v>
       </c>
       <c r="D96">
-        <v>38.19318831247001</v>
+        <v>37.82489416119753</v>
       </c>
       <c r="E96">
-        <v>157.902</v>
+        <v>161.135</v>
       </c>
       <c r="F96">
-        <v>303.902</v>
+        <v>307.135</v>
       </c>
       <c r="G96">
         <v>6.76</v>
@@ -9153,37 +9153,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M96">
-        <v>71.66009160000002</v>
+        <v>72.42243300000001</v>
       </c>
       <c r="N96">
-        <v>-57.69342493333335</v>
+        <v>-58.45576633333335</v>
       </c>
       <c r="O96">
-        <v>-13.846421984</v>
+        <v>-14.02938392</v>
       </c>
       <c r="P96">
-        <v>-43.84700294933335</v>
+        <v>-44.42638241333334</v>
       </c>
       <c r="Q96">
-        <v>-7.147002949333348</v>
+        <v>-7.72638241333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4941945951879096</v>
+        <v>0.5838735142254917</v>
       </c>
       <c r="T96">
-        <v>9.219464820552012</v>
+        <v>11.06335778466242</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04677638452809343</v>
+        <v>0.04628400153306087</v>
       </c>
       <c r="W96">
-        <v>0.2247701285282756</v>
+        <v>0.2248862324385043</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1949016022003893</v>
+        <v>0.1928500063877536</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2428355965278536</v>
+        <v>0.2447355965278536</v>
       </c>
       <c r="C97">
-        <v>-262.5501058388026</v>
+        <v>-266.1443649606521</v>
       </c>
       <c r="D97">
-        <v>37.82489416119753</v>
+        <v>37.46363503934797</v>
       </c>
       <c r="E97">
-        <v>161.135</v>
+        <v>164.3680000000001</v>
       </c>
       <c r="F97">
-        <v>307.135</v>
+        <v>310.3680000000001</v>
       </c>
       <c r="G97">
         <v>6.76</v>
@@ -9235,37 +9235,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M97">
-        <v>72.42243300000001</v>
+        <v>73.18477440000001</v>
       </c>
       <c r="N97">
-        <v>-58.45576633333335</v>
+        <v>-59.21810773333335</v>
       </c>
       <c r="O97">
-        <v>-14.02938392</v>
+        <v>-14.212345856</v>
       </c>
       <c r="P97">
-        <v>-44.42638241333334</v>
+        <v>-45.00576187733334</v>
       </c>
       <c r="Q97">
-        <v>-7.72638241333334</v>
+        <v>-8.305761877333339</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5838735142254917</v>
+        <v>0.718391892781865</v>
       </c>
       <c r="T97">
-        <v>11.06335778466242</v>
+        <v>13.82919723082803</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04628400153306087</v>
+        <v>0.04580187651709149</v>
       </c>
       <c r="W97">
-        <v>0.2248862324385043</v>
+        <v>0.2249999175172699</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1928500063877536</v>
+        <v>0.1908411521545479</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2447355965278536</v>
+        <v>0.2466355965278536</v>
       </c>
       <c r="C98">
-        <v>-266.144364960652</v>
+        <v>-269.731788717224</v>
       </c>
       <c r="D98">
-        <v>37.46363503934797</v>
+        <v>37.10921128277603</v>
       </c>
       <c r="E98">
-        <v>164.368</v>
+        <v>167.601</v>
       </c>
       <c r="F98">
-        <v>310.368</v>
+        <v>313.601</v>
       </c>
       <c r="G98">
         <v>6.76</v>
@@ -9317,37 +9317,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M98">
-        <v>73.18477439999999</v>
+        <v>73.94711580000001</v>
       </c>
       <c r="N98">
-        <v>-59.21810773333333</v>
+        <v>-59.98044913333334</v>
       </c>
       <c r="O98">
-        <v>-14.212345856</v>
+        <v>-14.395307792</v>
       </c>
       <c r="P98">
-        <v>-45.00576187733333</v>
+        <v>-45.58514134133334</v>
       </c>
       <c r="Q98">
-        <v>-8.305761877333332</v>
+        <v>-8.885141341333338</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7183918927818631</v>
+        <v>0.9425891903758176</v>
       </c>
       <c r="T98">
-        <v>13.82919723082799</v>
+        <v>18.43892964110399</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0458018765170915</v>
+        <v>0.04532969222310086</v>
       </c>
       <c r="W98">
-        <v>0.2249999175172698</v>
+        <v>0.2251112585737928</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1908411521545479</v>
+        <v>0.1888737175962536</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2466355965278536</v>
+        <v>0.2485355965278536</v>
       </c>
       <c r="C99">
-        <v>-269.731788717224</v>
+        <v>-273.3125692878037</v>
       </c>
       <c r="D99">
-        <v>37.10921128277603</v>
+        <v>36.76143071219634</v>
       </c>
       <c r="E99">
-        <v>167.601</v>
+        <v>170.834</v>
       </c>
       <c r="F99">
-        <v>313.601</v>
+        <v>316.834</v>
       </c>
       <c r="G99">
         <v>6.76</v>
@@ -9399,37 +9399,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M99">
-        <v>73.94711580000001</v>
+        <v>74.7094572</v>
       </c>
       <c r="N99">
-        <v>-59.98044913333334</v>
+        <v>-60.74279053333334</v>
       </c>
       <c r="O99">
-        <v>-14.395307792</v>
+        <v>-14.578269728</v>
       </c>
       <c r="P99">
-        <v>-45.58514134133334</v>
+        <v>-46.16452080533334</v>
       </c>
       <c r="Q99">
-        <v>-8.885141341333338</v>
+        <v>-9.464520805333336</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9425891903758176</v>
+        <v>1.390983785563726</v>
       </c>
       <c r="T99">
-        <v>18.43892964110399</v>
+        <v>27.65839446165599</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04532969222310086</v>
+        <v>0.0448671443432733</v>
       </c>
       <c r="W99">
-        <v>0.2251112585737928</v>
+        <v>0.2252203273638562</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1888737175962536</v>
+        <v>0.1869464347636387</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2485355965278536</v>
+        <v>0.2504355965278536</v>
       </c>
       <c r="C100">
-        <v>-273.3125692878037</v>
+        <v>-276.8868917142939</v>
       </c>
       <c r="D100">
-        <v>36.76143071219634</v>
+        <v>36.42010828570609</v>
       </c>
       <c r="E100">
-        <v>170.834</v>
+        <v>174.067</v>
       </c>
       <c r="F100">
-        <v>316.834</v>
+        <v>320.067</v>
       </c>
       <c r="G100">
         <v>6.76</v>
@@ -9481,37 +9481,37 @@
         <v>13.96666666666666</v>
       </c>
       <c r="M100">
-        <v>74.7094572</v>
+        <v>75.4717986</v>
       </c>
       <c r="N100">
-        <v>-60.74279053333334</v>
+        <v>-61.50513193333334</v>
       </c>
       <c r="O100">
-        <v>-14.578269728</v>
+        <v>-14.761231664</v>
       </c>
       <c r="P100">
-        <v>-46.16452080533334</v>
+        <v>-46.74390026933334</v>
       </c>
       <c r="Q100">
-        <v>-9.464520805333336</v>
+        <v>-10.04390026933334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.390983785563726</v>
+        <v>2.736167571127452</v>
       </c>
       <c r="T100">
-        <v>27.65839446165599</v>
+        <v>55.31678892331198</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0448671443432733</v>
+        <v>0.04441394086505842</v>
       </c>
       <c r="W100">
-        <v>0.2252203273638562</v>
+        <v>0.2253271927440192</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1869464347636387</v>
+        <v>0.1850580869377434</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2504355965278536</v>
-      </c>
-      <c r="C101">
-        <v>-276.8868917142939</v>
-      </c>
-      <c r="D101">
-        <v>36.42010828570609</v>
-      </c>
-      <c r="E101">
-        <v>174.067</v>
-      </c>
-      <c r="F101">
-        <v>320.067</v>
-      </c>
-      <c r="G101">
-        <v>6.76</v>
-      </c>
-      <c r="H101">
-        <v>177.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>50.66666666666666</v>
-      </c>
-      <c r="K101">
-        <v>36.7</v>
-      </c>
-      <c r="L101">
-        <v>13.96666666666666</v>
-      </c>
-      <c r="M101">
-        <v>75.4717986</v>
-      </c>
-      <c r="N101">
-        <v>-61.50513193333334</v>
-      </c>
-      <c r="O101">
-        <v>-14.761231664</v>
-      </c>
-      <c r="P101">
-        <v>-46.74390026933334</v>
-      </c>
-      <c r="Q101">
-        <v>-10.04390026933334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.736167571127452</v>
-      </c>
-      <c r="T101">
-        <v>55.31678892331198</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04441394086505842</v>
-      </c>
-      <c r="W101">
-        <v>0.2253271927440192</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1850580869377434</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
